--- a/AAII_Financials/Yearly/TRP_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/TRP_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="92">
   <si>
     <t>TRP</t>
   </si>
@@ -656,197 +656,209 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41274</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40908</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>10888400</v>
+        <v>11775100</v>
       </c>
       <c r="E8" s="3">
-        <v>9732500</v>
+        <v>11067900</v>
       </c>
       <c r="F8" s="3">
-        <v>9450400</v>
+        <v>9892900</v>
       </c>
       <c r="G8" s="3">
-        <v>9636500</v>
+        <v>9606100</v>
       </c>
       <c r="H8" s="3">
-        <v>9944800</v>
+        <v>9795300</v>
       </c>
       <c r="I8" s="3">
-        <v>9777600</v>
+        <v>10108600</v>
       </c>
       <c r="J8" s="3">
+        <v>9938700</v>
+      </c>
+      <c r="K8" s="3">
         <v>9121800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>8524500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>7995700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>6772100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>6027600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>6022200</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>3585600</v>
+        <v>3611400</v>
       </c>
       <c r="E9" s="3">
-        <v>2979300</v>
+        <v>3644700</v>
       </c>
       <c r="F9" s="3">
-        <v>2819300</v>
+        <v>3028400</v>
       </c>
       <c r="G9" s="3">
-        <v>2841900</v>
+        <v>2865800</v>
       </c>
       <c r="H9" s="3">
-        <v>2610700</v>
+        <v>2888700</v>
       </c>
       <c r="I9" s="3">
-        <v>2839700</v>
+        <v>2653700</v>
       </c>
       <c r="J9" s="3">
+        <v>2886500</v>
+      </c>
+      <c r="K9" s="3">
         <v>2807000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2480100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2334000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2058500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1939900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2572800</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>7302800</v>
+        <v>8163600</v>
       </c>
       <c r="E10" s="3">
-        <v>6753200</v>
+        <v>7423200</v>
       </c>
       <c r="F10" s="3">
-        <v>6631100</v>
+        <v>6864500</v>
       </c>
       <c r="G10" s="3">
-        <v>6794600</v>
+        <v>6740300</v>
       </c>
       <c r="H10" s="3">
-        <v>7334100</v>
+        <v>6906600</v>
       </c>
       <c r="I10" s="3">
-        <v>6937900</v>
+        <v>7454900</v>
       </c>
       <c r="J10" s="3">
+        <v>7052200</v>
+      </c>
+      <c r="K10" s="3">
         <v>6314800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>6044400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>5661800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>4713600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4087600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>3449400</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -863,8 +875,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -904,9 +917,12 @@
       <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -946,41 +962,44 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>2545300</v>
+        <v>1575500</v>
       </c>
       <c r="E14" s="3">
-        <v>2017500</v>
+        <v>2587200</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>2050700</v>
       </c>
       <c r="G14" s="3">
         <v>0</v>
       </c>
       <c r="H14" s="3">
-        <v>582300</v>
+        <v>0</v>
       </c>
       <c r="I14" s="3">
-        <v>913900</v>
+        <v>591900</v>
       </c>
       <c r="J14" s="3">
+        <v>928900</v>
+      </c>
+      <c r="K14" s="3">
         <v>1088300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>2827700</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>8</v>
@@ -988,51 +1007,57 @@
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>1878600</v>
+        <v>2052900</v>
       </c>
       <c r="E15" s="3">
-        <v>1833500</v>
+        <v>1909600</v>
       </c>
       <c r="F15" s="3">
-        <v>1883000</v>
+        <v>1863700</v>
       </c>
       <c r="G15" s="3">
-        <v>1791400</v>
+        <v>1914000</v>
       </c>
       <c r="H15" s="3">
-        <v>1708500</v>
+        <v>1820900</v>
       </c>
       <c r="I15" s="3">
-        <v>1494000</v>
+        <v>1736600</v>
       </c>
       <c r="J15" s="3">
+        <v>1518600</v>
+      </c>
+      <c r="K15" s="3">
         <v>1409700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1325300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1264700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1143200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1035100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1020200</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1046,92 +1071,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>9014200</v>
+        <v>8284800</v>
       </c>
       <c r="E17" s="3">
-        <v>7456200</v>
+        <v>9162700</v>
       </c>
       <c r="F17" s="3">
-        <v>5230800</v>
+        <v>7579100</v>
       </c>
       <c r="G17" s="3">
-        <v>5430000</v>
+        <v>5317000</v>
       </c>
       <c r="H17" s="3">
-        <v>6397000</v>
+        <v>5519500</v>
       </c>
       <c r="I17" s="3">
-        <v>7393000</v>
+        <v>6502400</v>
       </c>
       <c r="J17" s="3">
+        <v>7514800</v>
+      </c>
+      <c r="K17" s="3">
         <v>7287500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>8701000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5411300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4558100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4091400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3908000</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1874200</v>
+        <v>3490200</v>
       </c>
       <c r="E18" s="3">
-        <v>2276300</v>
+        <v>1905100</v>
       </c>
       <c r="F18" s="3">
-        <v>4219600</v>
+        <v>2313800</v>
       </c>
       <c r="G18" s="3">
-        <v>4206500</v>
+        <v>4289100</v>
       </c>
       <c r="H18" s="3">
-        <v>3547800</v>
+        <v>4275800</v>
       </c>
       <c r="I18" s="3">
-        <v>2384600</v>
+        <v>3606300</v>
       </c>
       <c r="J18" s="3">
+        <v>2423900</v>
+      </c>
+      <c r="K18" s="3">
         <v>1834200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-176500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2584400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2214000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1936200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2114200</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1148,218 +1180,234 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>1006200</v>
+        <v>1877000</v>
       </c>
       <c r="E20" s="3">
-        <v>1014200</v>
+        <v>1022800</v>
       </c>
       <c r="F20" s="3">
-        <v>1113100</v>
+        <v>1030900</v>
       </c>
       <c r="G20" s="3">
-        <v>1260600</v>
+        <v>1131400</v>
       </c>
       <c r="H20" s="3">
-        <v>969800</v>
+        <v>1281400</v>
       </c>
       <c r="I20" s="3">
-        <v>1522400</v>
+        <v>985800</v>
       </c>
       <c r="J20" s="3">
+        <v>1547400</v>
+      </c>
+      <c r="K20" s="3">
         <v>143200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>461800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>573100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>501900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-310900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>399500</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>4769600</v>
+        <v>7429800</v>
       </c>
       <c r="E21" s="3">
-        <v>5134300</v>
+        <v>4846400</v>
       </c>
       <c r="F21" s="3">
-        <v>7226200</v>
+        <v>5217100</v>
       </c>
       <c r="G21" s="3">
-        <v>7268500</v>
+        <v>7343400</v>
       </c>
       <c r="H21" s="3">
-        <v>6235700</v>
+        <v>7386600</v>
       </c>
       <c r="I21" s="3">
-        <v>5409400</v>
+        <v>6336800</v>
       </c>
       <c r="J21" s="3">
+        <v>5497100</v>
+      </c>
+      <c r="K21" s="3">
         <v>3395100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1590200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>4417500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3857100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2660800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3538700</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>1881500</v>
+        <v>2403900</v>
       </c>
       <c r="E22" s="3">
-        <v>1715700</v>
+        <v>1912500</v>
       </c>
       <c r="F22" s="3">
-        <v>1619800</v>
+        <v>1744000</v>
       </c>
       <c r="G22" s="3">
-        <v>1696100</v>
+        <v>1646500</v>
       </c>
       <c r="H22" s="3">
-        <v>1646700</v>
+        <v>1724100</v>
       </c>
       <c r="I22" s="3">
-        <v>1503500</v>
+        <v>1673800</v>
       </c>
       <c r="J22" s="3">
+        <v>1528200</v>
+      </c>
+      <c r="K22" s="3">
         <v>1369000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1115800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>940500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>774400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>166400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>758200</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>998900</v>
+        <v>2963300</v>
       </c>
       <c r="E23" s="3">
-        <v>1574700</v>
+        <v>1015400</v>
       </c>
       <c r="F23" s="3">
-        <v>3712800</v>
+        <v>1600700</v>
       </c>
       <c r="G23" s="3">
-        <v>3771000</v>
+        <v>3774000</v>
       </c>
       <c r="H23" s="3">
-        <v>2871000</v>
+        <v>3833100</v>
       </c>
       <c r="I23" s="3">
-        <v>2403500</v>
+        <v>2918300</v>
       </c>
       <c r="J23" s="3">
+        <v>2443100</v>
+      </c>
+      <c r="K23" s="3">
         <v>608500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-830500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2217000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1941500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1458900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1755400</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>428200</v>
+        <v>696100</v>
       </c>
       <c r="E24" s="3">
-        <v>87200</v>
+        <v>435300</v>
       </c>
       <c r="F24" s="3">
-        <v>141000</v>
+        <v>88700</v>
       </c>
       <c r="G24" s="3">
-        <v>548200</v>
+        <v>143400</v>
       </c>
       <c r="H24" s="3">
-        <v>435500</v>
+        <v>557200</v>
       </c>
       <c r="I24" s="3">
-        <v>519800</v>
+        <v>442700</v>
       </c>
       <c r="J24" s="3">
+        <v>528400</v>
+      </c>
+      <c r="K24" s="3">
         <v>255900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>25500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>652400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>470400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>350800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>441700</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1399,93 +1447,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>570700</v>
+        <v>2267200</v>
       </c>
       <c r="E26" s="3">
-        <v>1487500</v>
+        <v>580100</v>
       </c>
       <c r="F26" s="3">
-        <v>3571800</v>
+        <v>1512000</v>
       </c>
       <c r="G26" s="3">
-        <v>3222800</v>
+        <v>3630700</v>
       </c>
       <c r="H26" s="3">
-        <v>2435500</v>
+        <v>3275900</v>
       </c>
       <c r="I26" s="3">
-        <v>1883700</v>
+        <v>2475600</v>
       </c>
       <c r="J26" s="3">
+        <v>1914700</v>
+      </c>
+      <c r="K26" s="3">
         <v>352600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-856000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1564600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1471100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1108100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1313700</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>466000</v>
+        <v>2090600</v>
       </c>
       <c r="E27" s="3">
-        <v>1319500</v>
+        <v>473700</v>
       </c>
       <c r="F27" s="3">
-        <v>3240300</v>
+        <v>1341300</v>
       </c>
       <c r="G27" s="3">
-        <v>2890600</v>
+        <v>3293700</v>
       </c>
       <c r="H27" s="3">
-        <v>2451500</v>
+        <v>2938200</v>
       </c>
       <c r="I27" s="3">
-        <v>1594300</v>
+        <v>2491900</v>
       </c>
       <c r="J27" s="3">
+        <v>1620600</v>
+      </c>
+      <c r="K27" s="3">
         <v>90100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-931100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1368300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1317900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>977900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1172300</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1525,9 +1582,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1537,26 +1597,26 @@
       <c r="E29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F29" s="3">
-        <v>0</v>
+      <c r="F29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G29" s="3">
         <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>121400</v>
+        <v>0</v>
       </c>
       <c r="I29" s="3">
-        <v>584500</v>
+        <v>123400</v>
       </c>
       <c r="J29" s="3">
-        <v>0</v>
+        <v>594100</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>8</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>8</v>
@@ -1567,9 +1627,12 @@
       <c r="O29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1609,9 +1672,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1651,93 +1717,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-1006200</v>
+        <v>-1877000</v>
       </c>
       <c r="E32" s="3">
-        <v>-1014200</v>
+        <v>-1022800</v>
       </c>
       <c r="F32" s="3">
-        <v>-1113100</v>
+        <v>-1030900</v>
       </c>
       <c r="G32" s="3">
-        <v>-1260600</v>
+        <v>-1131400</v>
       </c>
       <c r="H32" s="3">
-        <v>-969800</v>
+        <v>-1281400</v>
       </c>
       <c r="I32" s="3">
-        <v>-1522400</v>
+        <v>-985800</v>
       </c>
       <c r="J32" s="3">
+        <v>-1547400</v>
+      </c>
+      <c r="K32" s="3">
         <v>-143200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-461800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-573100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-501900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>310900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-399500</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>466000</v>
+        <v>2090600</v>
       </c>
       <c r="E33" s="3">
-        <v>1319500</v>
+        <v>473700</v>
       </c>
       <c r="F33" s="3">
-        <v>3240300</v>
+        <v>1341300</v>
       </c>
       <c r="G33" s="3">
-        <v>2890600</v>
+        <v>3293700</v>
       </c>
       <c r="H33" s="3">
-        <v>2572900</v>
+        <v>2938200</v>
       </c>
       <c r="I33" s="3">
-        <v>2178800</v>
+        <v>2615300</v>
       </c>
       <c r="J33" s="3">
+        <v>2214800</v>
+      </c>
+      <c r="K33" s="3">
         <v>90100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-931100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1368300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1317900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>977900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1172300</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1777,98 +1852,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>466000</v>
+        <v>2090600</v>
       </c>
       <c r="E35" s="3">
-        <v>1319500</v>
+        <v>473700</v>
       </c>
       <c r="F35" s="3">
-        <v>3240300</v>
+        <v>1341300</v>
       </c>
       <c r="G35" s="3">
-        <v>2890600</v>
+        <v>3293700</v>
       </c>
       <c r="H35" s="3">
-        <v>2572900</v>
+        <v>2938200</v>
       </c>
       <c r="I35" s="3">
-        <v>2178800</v>
+        <v>2615300</v>
       </c>
       <c r="J35" s="3">
+        <v>2214800</v>
+      </c>
+      <c r="K35" s="3">
         <v>90100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-931100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1368300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1317900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>977900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1172300</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41274</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40908</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1885,8 +1969,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1903,50 +1988,54 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>450700</v>
+        <v>2718000</v>
       </c>
       <c r="E41" s="3">
-        <v>489300</v>
+        <v>458200</v>
       </c>
       <c r="F41" s="3">
-        <v>1112300</v>
+        <v>497300</v>
       </c>
       <c r="G41" s="3">
-        <v>976400</v>
+        <v>1130700</v>
       </c>
       <c r="H41" s="3">
-        <v>324200</v>
+        <v>992500</v>
       </c>
       <c r="I41" s="3">
-        <v>791700</v>
+        <v>329600</v>
       </c>
       <c r="J41" s="3">
+        <v>804800</v>
+      </c>
+      <c r="K41" s="3">
         <v>738600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>638200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>383900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>713600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>414800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>502400</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1956,17 +2045,17 @@
       <c r="E42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F42" s="3">
-        <v>136700</v>
-      </c>
-      <c r="G42" s="3" t="s">
+      <c r="F42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H42" s="3">
-        <v>521300</v>
-      </c>
-      <c r="I42" s="3" t="s">
+      <c r="G42" s="3">
+        <v>138900</v>
+      </c>
+      <c r="H42" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="I42" s="3">
+        <v>529900</v>
       </c>
       <c r="J42" s="3" t="s">
         <v>8</v>
@@ -1983,306 +2072,330 @@
       <c r="N42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="O42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>2747400</v>
+        <v>3222000</v>
       </c>
       <c r="E43" s="3">
-        <v>3279500</v>
+        <v>2792600</v>
       </c>
       <c r="F43" s="3">
-        <v>1667800</v>
+        <v>3333600</v>
       </c>
       <c r="G43" s="3">
-        <v>1872100</v>
+        <v>1695200</v>
       </c>
       <c r="H43" s="3">
-        <v>1958600</v>
+        <v>1902900</v>
       </c>
       <c r="I43" s="3">
-        <v>1833500</v>
+        <v>1990800</v>
       </c>
       <c r="J43" s="3">
+        <v>1863700</v>
+      </c>
+      <c r="K43" s="3">
         <v>1508500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1041400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1030800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>863700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>791900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>840400</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>680500</v>
+        <v>725700</v>
       </c>
       <c r="E44" s="3">
-        <v>526400</v>
+        <v>691700</v>
       </c>
       <c r="F44" s="3">
-        <v>457300</v>
+        <v>535000</v>
       </c>
       <c r="G44" s="3">
-        <v>328600</v>
+        <v>464800</v>
       </c>
       <c r="H44" s="3">
-        <v>313300</v>
+        <v>334000</v>
       </c>
       <c r="I44" s="3">
-        <v>274800</v>
+        <v>318500</v>
       </c>
       <c r="J44" s="3">
+        <v>279300</v>
+      </c>
+      <c r="K44" s="3">
         <v>267500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>242500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>229200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>193200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>168600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>190500</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1451800</v>
+        <v>1738100</v>
       </c>
       <c r="E45" s="3">
-        <v>1101400</v>
+        <v>1475800</v>
       </c>
       <c r="F45" s="3">
-        <v>407100</v>
+        <v>1119600</v>
       </c>
       <c r="G45" s="3">
-        <v>2385300</v>
+        <v>413800</v>
       </c>
       <c r="H45" s="3">
-        <v>615800</v>
+        <v>2424600</v>
       </c>
       <c r="I45" s="3">
-        <v>502400</v>
+        <v>625900</v>
       </c>
       <c r="J45" s="3">
+        <v>510600</v>
+      </c>
+      <c r="K45" s="3">
         <v>3362400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1537800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1935100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>652000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>750500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>855800</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>5330400</v>
+        <v>8403800</v>
       </c>
       <c r="E46" s="3">
-        <v>5396600</v>
+        <v>5418300</v>
       </c>
       <c r="F46" s="3">
-        <v>3781200</v>
+        <v>5485500</v>
       </c>
       <c r="G46" s="3">
-        <v>5562400</v>
+        <v>3843500</v>
       </c>
       <c r="H46" s="3">
-        <v>3733200</v>
+        <v>5654000</v>
       </c>
       <c r="I46" s="3">
-        <v>3402400</v>
+        <v>3794700</v>
       </c>
       <c r="J46" s="3">
+        <v>3458500</v>
+      </c>
+      <c r="K46" s="3">
         <v>5877100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2941900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2443900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2422600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2125900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2389200</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>8567800</v>
+        <v>9632000</v>
       </c>
       <c r="E47" s="3">
-        <v>6490700</v>
+        <v>8709000</v>
       </c>
       <c r="F47" s="3">
-        <v>5980400</v>
+        <v>6597700</v>
       </c>
       <c r="G47" s="3">
-        <v>5772500</v>
+        <v>6078900</v>
       </c>
       <c r="H47" s="3">
-        <v>6163600</v>
+        <v>5867600</v>
       </c>
       <c r="I47" s="3">
-        <v>5346400</v>
+        <v>6265200</v>
       </c>
       <c r="J47" s="3">
+        <v>5434500</v>
+      </c>
+      <c r="K47" s="3">
         <v>4843300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>4879800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>4583100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>4660500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>4327800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>4236000</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>55209100</v>
+        <v>59539700</v>
       </c>
       <c r="E48" s="3">
-        <v>51023000</v>
+        <v>56118900</v>
       </c>
       <c r="F48" s="3">
-        <v>50727100</v>
+        <v>51863800</v>
       </c>
       <c r="G48" s="3">
-        <v>47611200</v>
+        <v>51563000</v>
       </c>
       <c r="H48" s="3">
-        <v>48348300</v>
+        <v>48395700</v>
       </c>
       <c r="I48" s="3">
-        <v>41641000</v>
+        <v>49145100</v>
       </c>
       <c r="J48" s="3">
+        <v>42327100</v>
+      </c>
+      <c r="K48" s="3">
         <v>39603900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>67302600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>65589400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>28949900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>25378800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>93656500</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>9337000</v>
+        <v>9261000</v>
       </c>
       <c r="E49" s="3">
-        <v>9147200</v>
+        <v>9490800</v>
       </c>
       <c r="F49" s="3">
-        <v>9217800</v>
+        <v>9298000</v>
       </c>
       <c r="G49" s="3">
-        <v>9369000</v>
+        <v>9369700</v>
       </c>
       <c r="H49" s="3">
-        <v>10307500</v>
+        <v>9523400</v>
       </c>
       <c r="I49" s="3">
-        <v>9512200</v>
+        <v>10477400</v>
       </c>
       <c r="J49" s="3">
+        <v>9668900</v>
+      </c>
+      <c r="K49" s="3">
         <v>10147600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>5981400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4603500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3534200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2886200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4594800</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2322,9 +2435,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2364,51 +2480,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>4687800</v>
+        <v>5562400</v>
       </c>
       <c r="E52" s="3">
-        <v>3709900</v>
+        <v>4765000</v>
       </c>
       <c r="F52" s="3">
-        <v>3212700</v>
+        <v>3771100</v>
       </c>
       <c r="G52" s="3">
-        <v>3861900</v>
+        <v>3265600</v>
       </c>
       <c r="H52" s="3">
-        <v>3363100</v>
+        <v>3925500</v>
       </c>
       <c r="I52" s="3">
-        <v>2694300</v>
+        <v>3418600</v>
       </c>
       <c r="J52" s="3">
+        <v>2738700</v>
+      </c>
+      <c r="K52" s="3">
         <v>3542000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3169400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1733400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1924500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1665900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1738500</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2448,51 +2570,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>83132100</v>
+        <v>92398900</v>
       </c>
       <c r="E54" s="3">
-        <v>75767500</v>
+        <v>84502000</v>
       </c>
       <c r="F54" s="3">
-        <v>72919100</v>
+        <v>77016100</v>
       </c>
       <c r="G54" s="3">
-        <v>72176800</v>
+        <v>74120700</v>
       </c>
       <c r="H54" s="3">
-        <v>71915800</v>
+        <v>73366200</v>
       </c>
       <c r="I54" s="3">
-        <v>62596300</v>
+        <v>73100900</v>
       </c>
       <c r="J54" s="3">
+        <v>63627800</v>
+      </c>
+      <c r="K54" s="3">
         <v>64014000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>48353900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>45945100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>41491800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>36384600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>36366500</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2509,8 +2637,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2527,260 +2656,279 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>4010900</v>
+        <v>3661000</v>
       </c>
       <c r="E57" s="3">
-        <v>3041100</v>
+        <v>4077000</v>
       </c>
       <c r="F57" s="3">
-        <v>2222500</v>
+        <v>3091200</v>
       </c>
       <c r="G57" s="3">
-        <v>2713900</v>
+        <v>2259100</v>
       </c>
       <c r="H57" s="3">
-        <v>2831700</v>
+        <v>2758600</v>
       </c>
       <c r="I57" s="3">
-        <v>2668100</v>
+        <v>2878400</v>
       </c>
       <c r="J57" s="3">
+        <v>2712100</v>
+      </c>
+      <c r="K57" s="3">
         <v>2006500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2745900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1274900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>666700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>694800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>534700</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>5932400</v>
+        <v>2171200</v>
       </c>
       <c r="E58" s="3">
-        <v>4715400</v>
+        <v>6030200</v>
       </c>
       <c r="F58" s="3">
-        <v>4469700</v>
+        <v>4793100</v>
       </c>
       <c r="G58" s="3">
-        <v>5092700</v>
+        <v>4543300</v>
       </c>
       <c r="H58" s="3">
-        <v>4524900</v>
+        <v>5176600</v>
       </c>
       <c r="I58" s="3">
-        <v>3365300</v>
+        <v>4599500</v>
       </c>
       <c r="J58" s="3">
+        <v>3420800</v>
+      </c>
+      <c r="K58" s="3">
         <v>1899000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2827000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3347500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2167000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2385600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2174900</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2348200</v>
+        <v>2900500</v>
       </c>
       <c r="E59" s="3">
-        <v>1724500</v>
+        <v>2386900</v>
       </c>
       <c r="F59" s="3">
-        <v>2022500</v>
+        <v>1752900</v>
       </c>
       <c r="G59" s="3">
-        <v>1571100</v>
+        <v>2055900</v>
       </c>
       <c r="H59" s="3">
-        <v>2055300</v>
+        <v>1597000</v>
       </c>
       <c r="I59" s="3">
-        <v>1147200</v>
+        <v>2089100</v>
       </c>
       <c r="J59" s="3">
+        <v>1166100</v>
+      </c>
+      <c r="K59" s="3">
         <v>1677900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1528000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1331400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1291000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1346700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1558000</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>12291600</v>
+        <v>8732600</v>
       </c>
       <c r="E60" s="3">
-        <v>9480900</v>
+        <v>12494100</v>
       </c>
       <c r="F60" s="3">
-        <v>8714700</v>
+        <v>9637200</v>
       </c>
       <c r="G60" s="3">
-        <v>9377700</v>
+        <v>8858300</v>
       </c>
       <c r="H60" s="3">
-        <v>9411900</v>
+        <v>9532200</v>
       </c>
       <c r="I60" s="3">
-        <v>7180700</v>
+        <v>9567000</v>
       </c>
       <c r="J60" s="3">
+        <v>7299000</v>
+      </c>
+      <c r="K60" s="3">
         <v>5583400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5527800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5950700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4124700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4427200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4242200</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>36452300</v>
+        <v>44533800</v>
       </c>
       <c r="E61" s="3">
-        <v>33646000</v>
+        <v>37053000</v>
       </c>
       <c r="F61" s="3">
-        <v>31560200</v>
+        <v>34200500</v>
       </c>
       <c r="G61" s="3">
-        <v>31184400</v>
+        <v>32080300</v>
       </c>
       <c r="H61" s="3">
-        <v>32000800</v>
+        <v>31698200</v>
       </c>
       <c r="I61" s="3">
-        <v>28267600</v>
+        <v>32528100</v>
       </c>
       <c r="J61" s="3">
+        <v>28733400</v>
+      </c>
+      <c r="K61" s="3">
         <v>30711100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>23515400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>18935400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>17671200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>14312800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>14396600</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>9585600</v>
+        <v>10306000</v>
       </c>
       <c r="E62" s="3">
-        <v>8361300</v>
+        <v>9743600</v>
       </c>
       <c r="F62" s="3">
-        <v>8309000</v>
+        <v>8499100</v>
       </c>
       <c r="G62" s="3">
-        <v>8061800</v>
+        <v>8445900</v>
       </c>
       <c r="H62" s="3">
-        <v>7970900</v>
+        <v>8194700</v>
       </c>
       <c r="I62" s="3">
-        <v>7598000</v>
+        <v>8102300</v>
       </c>
       <c r="J62" s="3">
+        <v>7723200</v>
+      </c>
+      <c r="K62" s="3">
         <v>8829500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>6624800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>4845300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>4194700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3841500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>4414200</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2820,9 +2968,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2862,9 +3013,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2904,51 +3058,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>58421100</v>
+        <v>70559500</v>
       </c>
       <c r="E66" s="3">
-        <v>51579200</v>
+        <v>59383800</v>
       </c>
       <c r="F66" s="3">
-        <v>50092400</v>
+        <v>52429100</v>
       </c>
       <c r="G66" s="3">
-        <v>49811800</v>
+        <v>50917900</v>
       </c>
       <c r="H66" s="3">
-        <v>50586800</v>
+        <v>50632600</v>
       </c>
       <c r="I66" s="3">
-        <v>44392700</v>
+        <v>51420400</v>
       </c>
       <c r="J66" s="3">
+        <v>45124200</v>
+      </c>
+      <c r="K66" s="3">
         <v>46378900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>36011200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>30974100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>27230800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>23654200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>23464800</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2965,8 +3125,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3006,9 +3167,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3048,51 +3212,57 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>1816800</v>
+        <v>1846700</v>
       </c>
       <c r="E70" s="3">
-        <v>2535100</v>
+        <v>1846700</v>
       </c>
       <c r="F70" s="3">
+        <v>2576900</v>
+      </c>
+      <c r="G70" s="3">
+        <v>2941200</v>
+      </c>
+      <c r="H70" s="3">
+        <v>2941200</v>
+      </c>
+      <c r="I70" s="3">
+        <v>2941200</v>
+      </c>
+      <c r="J70" s="3">
+        <v>2941200</v>
+      </c>
+      <c r="K70" s="3">
         <v>2893500</v>
       </c>
-      <c r="G70" s="3">
-        <v>2893500</v>
-      </c>
-      <c r="H70" s="3">
-        <v>2893500</v>
-      </c>
-      <c r="I70" s="3">
-        <v>2893500</v>
-      </c>
-      <c r="J70" s="3">
-        <v>2893500</v>
-      </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>1876400</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>1770300</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="3">
         <v>1395700</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="3">
         <v>921400</v>
       </c>
-      <c r="O70" s="3">
+      <c r="P70" s="3">
         <v>1880600</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3132,51 +3302,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>595400</v>
+        <v>-2214800</v>
       </c>
       <c r="E72" s="3">
-        <v>2743000</v>
+        <v>605200</v>
       </c>
       <c r="F72" s="3">
-        <v>3901900</v>
+        <v>2788200</v>
       </c>
       <c r="G72" s="3">
-        <v>2875300</v>
+        <v>3966200</v>
       </c>
       <c r="H72" s="3">
-        <v>2016000</v>
+        <v>2922700</v>
       </c>
       <c r="I72" s="3">
-        <v>1179900</v>
+        <v>2049200</v>
       </c>
       <c r="J72" s="3">
+        <v>1199400</v>
+      </c>
+      <c r="K72" s="3">
         <v>827300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2079100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>4300500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>3923000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3528300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>3555400</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3216,9 +3392,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3258,9 +3437,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3300,51 +3482,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>22894300</v>
+        <v>19992700</v>
       </c>
       <c r="E76" s="3">
-        <v>21653200</v>
+        <v>23271600</v>
       </c>
       <c r="F76" s="3">
-        <v>19933200</v>
+        <v>22010000</v>
       </c>
       <c r="G76" s="3">
-        <v>19471500</v>
+        <v>20261600</v>
       </c>
       <c r="H76" s="3">
-        <v>18435500</v>
+        <v>19792300</v>
       </c>
       <c r="I76" s="3">
-        <v>15310100</v>
+        <v>18739300</v>
       </c>
       <c r="J76" s="3">
+        <v>15562400</v>
+      </c>
+      <c r="K76" s="3">
         <v>14741600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>10466200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>13200600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>12865200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>11809000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>11021100</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3384,98 +3572,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41274</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40908</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>466000</v>
+        <v>2090600</v>
       </c>
       <c r="E81" s="3">
-        <v>1319500</v>
+        <v>473700</v>
       </c>
       <c r="F81" s="3">
-        <v>3240300</v>
+        <v>1341300</v>
       </c>
       <c r="G81" s="3">
-        <v>2890600</v>
+        <v>3293700</v>
       </c>
       <c r="H81" s="3">
-        <v>2572900</v>
+        <v>2938200</v>
       </c>
       <c r="I81" s="3">
-        <v>2178800</v>
+        <v>2615300</v>
       </c>
       <c r="J81" s="3">
+        <v>2214800</v>
+      </c>
+      <c r="K81" s="3">
         <v>90100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-931100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1368300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1317900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>977900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1172300</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3492,50 +3689,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1878600</v>
+        <v>2052900</v>
       </c>
       <c r="E83" s="3">
-        <v>1833500</v>
+        <v>1909600</v>
       </c>
       <c r="F83" s="3">
-        <v>1883000</v>
+        <v>1863700</v>
       </c>
       <c r="G83" s="3">
-        <v>1791400</v>
+        <v>1914000</v>
       </c>
       <c r="H83" s="3">
-        <v>1708500</v>
+        <v>1820900</v>
       </c>
       <c r="I83" s="3">
-        <v>1494000</v>
+        <v>1736600</v>
       </c>
       <c r="J83" s="3">
+        <v>1518600</v>
+      </c>
+      <c r="K83" s="3">
         <v>1409700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1325300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1264700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1143200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1035100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1020200</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3575,9 +3776,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3617,9 +3821,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3659,9 +3866,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3701,9 +3911,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3743,51 +3956,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>4634700</v>
+        <v>5371000</v>
       </c>
       <c r="E89" s="3">
-        <v>5009100</v>
+        <v>4711100</v>
       </c>
       <c r="F89" s="3">
-        <v>5131200</v>
+        <v>5091600</v>
       </c>
       <c r="G89" s="3">
-        <v>5148700</v>
+        <v>5215800</v>
       </c>
       <c r="H89" s="3">
-        <v>4765600</v>
+        <v>5233500</v>
       </c>
       <c r="I89" s="3">
-        <v>3802300</v>
+        <v>4844100</v>
       </c>
       <c r="J89" s="3">
+        <v>3864900</v>
+      </c>
+      <c r="K89" s="3">
         <v>3685200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3089800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3202200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2828300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2688200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2831700</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3804,50 +4023,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-4890600</v>
+        <v>-6022000</v>
       </c>
       <c r="E91" s="3">
-        <v>-4306800</v>
+        <v>-4971200</v>
       </c>
       <c r="F91" s="3">
-        <v>-5914200</v>
+        <v>-4377800</v>
       </c>
       <c r="G91" s="3">
-        <v>-5948400</v>
+        <v>-6011700</v>
       </c>
       <c r="H91" s="3">
-        <v>-7207600</v>
+        <v>-6046400</v>
       </c>
       <c r="I91" s="3">
-        <v>-5473700</v>
+        <v>-7326300</v>
       </c>
       <c r="J91" s="3">
+        <v>-5563900</v>
+      </c>
+      <c r="K91" s="3">
         <v>-3854600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3325600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3420500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3434200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1953500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1930600</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3887,9 +4110,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3929,51 +4155,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-5095600</v>
+        <v>-9080000</v>
       </c>
       <c r="E94" s="3">
-        <v>-5606700</v>
+        <v>-5179600</v>
       </c>
       <c r="F94" s="3">
-        <v>-4399900</v>
+        <v>-5699100</v>
       </c>
       <c r="G94" s="3">
-        <v>-4996000</v>
+        <v>-4472400</v>
       </c>
       <c r="H94" s="3">
-        <v>-7283900</v>
+        <v>-5078300</v>
       </c>
       <c r="I94" s="3">
-        <v>-2689200</v>
+        <v>-7403900</v>
       </c>
       <c r="J94" s="3">
+        <v>-2733500</v>
+      </c>
+      <c r="K94" s="3">
         <v>-13655400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3461500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3253200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-3941500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2451100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2346200</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3990,50 +4222,54 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-2397700</v>
+        <v>-2127600</v>
       </c>
       <c r="E96" s="3">
-        <v>-2514000</v>
+        <v>-2437200</v>
       </c>
       <c r="F96" s="3">
-        <v>-2287200</v>
+        <v>-2555400</v>
       </c>
       <c r="G96" s="3">
-        <v>-1423500</v>
+        <v>-2324900</v>
       </c>
       <c r="H96" s="3">
-        <v>-1257000</v>
+        <v>-1446900</v>
       </c>
       <c r="I96" s="3">
-        <v>-1086200</v>
+        <v>-1277700</v>
       </c>
       <c r="J96" s="3">
+        <v>-1104100</v>
+      </c>
+      <c r="K96" s="3">
         <v>-1116700</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-1154800</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-1129700</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-1043900</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-964300</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-1561000</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4073,9 +4309,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4115,9 +4354,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4157,133 +4399,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>354100</v>
+        <v>5980600</v>
       </c>
       <c r="E100" s="3">
-        <v>-64000</v>
+        <v>359900</v>
       </c>
       <c r="F100" s="3">
-        <v>-581600</v>
+        <v>-65000</v>
       </c>
       <c r="G100" s="3">
-        <v>503800</v>
+        <v>-591200</v>
       </c>
       <c r="H100" s="3">
-        <v>1997800</v>
+        <v>512100</v>
       </c>
       <c r="I100" s="3">
-        <v>-1031600</v>
+        <v>2030700</v>
       </c>
       <c r="J100" s="3">
+        <v>-1048600</v>
+      </c>
+      <c r="K100" s="3">
         <v>10183200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>558600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-292800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1381100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-303400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-493200</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>68300</v>
+        <v>-11800</v>
       </c>
       <c r="E101" s="3">
-        <v>38500</v>
+        <v>69500</v>
       </c>
       <c r="F101" s="3">
-        <v>-13800</v>
+        <v>39200</v>
       </c>
       <c r="G101" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="H101" s="3">
         <v>-4400</v>
       </c>
-      <c r="H101" s="3">
-        <v>53100</v>
-      </c>
       <c r="I101" s="3">
-        <v>-28400</v>
+        <v>53900</v>
       </c>
       <c r="J101" s="3">
+        <v>-28800</v>
+      </c>
+      <c r="K101" s="3">
         <v>-92300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>84100</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
       <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
         <v>21600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-11300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>3100</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-38500</v>
+        <v>2259800</v>
       </c>
       <c r="E102" s="3">
-        <v>-623000</v>
+        <v>-39200</v>
       </c>
       <c r="F102" s="3">
-        <v>136000</v>
+        <v>-633300</v>
       </c>
       <c r="G102" s="3">
-        <v>652100</v>
+        <v>138200</v>
       </c>
       <c r="H102" s="3">
-        <v>-467500</v>
+        <v>662900</v>
       </c>
       <c r="I102" s="3">
-        <v>53100</v>
+        <v>-475200</v>
       </c>
       <c r="J102" s="3">
+        <v>53900</v>
+      </c>
+      <c r="K102" s="3">
         <v>120700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>271100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-343900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>289500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-77500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-4600</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/TRP_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/TRP_YR_FIN.xlsx
@@ -728,25 +728,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>11775100</v>
+        <v>11612100</v>
       </c>
       <c r="E8" s="3">
-        <v>11067900</v>
+        <v>10914600</v>
       </c>
       <c r="F8" s="3">
-        <v>9892900</v>
+        <v>9755900</v>
       </c>
       <c r="G8" s="3">
-        <v>9606100</v>
+        <v>9473200</v>
       </c>
       <c r="H8" s="3">
-        <v>9795300</v>
+        <v>9659700</v>
       </c>
       <c r="I8" s="3">
-        <v>10108600</v>
+        <v>9968700</v>
       </c>
       <c r="J8" s="3">
-        <v>9938700</v>
+        <v>9801100</v>
       </c>
       <c r="K8" s="3">
         <v>9121800</v>
@@ -773,25 +773,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>3611400</v>
+        <v>3561500</v>
       </c>
       <c r="E9" s="3">
-        <v>3644700</v>
+        <v>3594200</v>
       </c>
       <c r="F9" s="3">
-        <v>3028400</v>
+        <v>2986500</v>
       </c>
       <c r="G9" s="3">
-        <v>2865800</v>
+        <v>2826100</v>
       </c>
       <c r="H9" s="3">
-        <v>2888700</v>
+        <v>2848700</v>
       </c>
       <c r="I9" s="3">
-        <v>2653700</v>
+        <v>2617000</v>
       </c>
       <c r="J9" s="3">
-        <v>2886500</v>
+        <v>2846500</v>
       </c>
       <c r="K9" s="3">
         <v>2807000</v>
@@ -818,25 +818,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>8163600</v>
+        <v>8050600</v>
       </c>
       <c r="E10" s="3">
-        <v>7423200</v>
+        <v>7320400</v>
       </c>
       <c r="F10" s="3">
-        <v>6864500</v>
+        <v>6769500</v>
       </c>
       <c r="G10" s="3">
-        <v>6740300</v>
+        <v>6647000</v>
       </c>
       <c r="H10" s="3">
-        <v>6906600</v>
+        <v>6811000</v>
       </c>
       <c r="I10" s="3">
-        <v>7454900</v>
+        <v>7351700</v>
       </c>
       <c r="J10" s="3">
-        <v>7052200</v>
+        <v>6954600</v>
       </c>
       <c r="K10" s="3">
         <v>6314800</v>
@@ -972,13 +972,13 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>1575500</v>
+        <v>1553700</v>
       </c>
       <c r="E14" s="3">
-        <v>2587200</v>
+        <v>2551400</v>
       </c>
       <c r="F14" s="3">
-        <v>2050700</v>
+        <v>2022300</v>
       </c>
       <c r="G14" s="3">
         <v>0</v>
@@ -987,10 +987,10 @@
         <v>0</v>
       </c>
       <c r="I14" s="3">
-        <v>591900</v>
+        <v>583700</v>
       </c>
       <c r="J14" s="3">
-        <v>928900</v>
+        <v>916100</v>
       </c>
       <c r="K14" s="3">
         <v>1088300</v>
@@ -1017,25 +1017,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>2052900</v>
+        <v>2024500</v>
       </c>
       <c r="E15" s="3">
-        <v>1909600</v>
+        <v>1883100</v>
       </c>
       <c r="F15" s="3">
-        <v>1863700</v>
+        <v>1837900</v>
       </c>
       <c r="G15" s="3">
-        <v>1914000</v>
+        <v>1887500</v>
       </c>
       <c r="H15" s="3">
-        <v>1820900</v>
+        <v>1795700</v>
       </c>
       <c r="I15" s="3">
-        <v>1736600</v>
+        <v>1712600</v>
       </c>
       <c r="J15" s="3">
-        <v>1518600</v>
+        <v>1497600</v>
       </c>
       <c r="K15" s="3">
         <v>1409700</v>
@@ -1078,25 +1078,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>8284800</v>
+        <v>8170100</v>
       </c>
       <c r="E17" s="3">
-        <v>9162700</v>
+        <v>9035900</v>
       </c>
       <c r="F17" s="3">
-        <v>7579100</v>
+        <v>7474200</v>
       </c>
       <c r="G17" s="3">
-        <v>5317000</v>
+        <v>5243400</v>
       </c>
       <c r="H17" s="3">
-        <v>5519500</v>
+        <v>5443100</v>
       </c>
       <c r="I17" s="3">
-        <v>6502400</v>
+        <v>6412400</v>
       </c>
       <c r="J17" s="3">
-        <v>7514800</v>
+        <v>7410800</v>
       </c>
       <c r="K17" s="3">
         <v>7287500</v>
@@ -1123,25 +1123,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>3490200</v>
+        <v>3441900</v>
       </c>
       <c r="E18" s="3">
-        <v>1905100</v>
+        <v>1878700</v>
       </c>
       <c r="F18" s="3">
-        <v>2313800</v>
+        <v>2281700</v>
       </c>
       <c r="G18" s="3">
-        <v>4289100</v>
+        <v>4229700</v>
       </c>
       <c r="H18" s="3">
-        <v>4275800</v>
+        <v>4216600</v>
       </c>
       <c r="I18" s="3">
-        <v>3606300</v>
+        <v>3556300</v>
       </c>
       <c r="J18" s="3">
-        <v>2423900</v>
+        <v>2390300</v>
       </c>
       <c r="K18" s="3">
         <v>1834200</v>
@@ -1187,25 +1187,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>1877000</v>
+        <v>1851100</v>
       </c>
       <c r="E20" s="3">
-        <v>1022800</v>
+        <v>1008600</v>
       </c>
       <c r="F20" s="3">
-        <v>1030900</v>
+        <v>1016600</v>
       </c>
       <c r="G20" s="3">
-        <v>1131400</v>
+        <v>1115700</v>
       </c>
       <c r="H20" s="3">
-        <v>1281400</v>
+        <v>1263700</v>
       </c>
       <c r="I20" s="3">
-        <v>985800</v>
+        <v>972200</v>
       </c>
       <c r="J20" s="3">
-        <v>1547400</v>
+        <v>1526000</v>
       </c>
       <c r="K20" s="3">
         <v>143200</v>
@@ -1232,25 +1232,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>7429800</v>
+        <v>7312300</v>
       </c>
       <c r="E21" s="3">
-        <v>4846400</v>
+        <v>4765700</v>
       </c>
       <c r="F21" s="3">
-        <v>5217100</v>
+        <v>5131600</v>
       </c>
       <c r="G21" s="3">
-        <v>7343400</v>
+        <v>7228100</v>
       </c>
       <c r="H21" s="3">
-        <v>7386600</v>
+        <v>7271400</v>
       </c>
       <c r="I21" s="3">
-        <v>6336800</v>
+        <v>6236700</v>
       </c>
       <c r="J21" s="3">
-        <v>5497100</v>
+        <v>5410100</v>
       </c>
       <c r="K21" s="3">
         <v>3395100</v>
@@ -1277,25 +1277,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>2403900</v>
+        <v>2370700</v>
       </c>
       <c r="E22" s="3">
-        <v>1912500</v>
+        <v>1886000</v>
       </c>
       <c r="F22" s="3">
-        <v>1744000</v>
+        <v>1719900</v>
       </c>
       <c r="G22" s="3">
-        <v>1646500</v>
+        <v>1623700</v>
       </c>
       <c r="H22" s="3">
-        <v>1724100</v>
+        <v>1700200</v>
       </c>
       <c r="I22" s="3">
-        <v>1673800</v>
+        <v>1650600</v>
       </c>
       <c r="J22" s="3">
-        <v>1528200</v>
+        <v>1507100</v>
       </c>
       <c r="K22" s="3">
         <v>1369000</v>
@@ -1322,25 +1322,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>2963300</v>
+        <v>2922300</v>
       </c>
       <c r="E23" s="3">
-        <v>1015400</v>
+        <v>1001300</v>
       </c>
       <c r="F23" s="3">
-        <v>1600700</v>
+        <v>1578500</v>
       </c>
       <c r="G23" s="3">
-        <v>3774000</v>
+        <v>3721800</v>
       </c>
       <c r="H23" s="3">
-        <v>3833100</v>
+        <v>3780100</v>
       </c>
       <c r="I23" s="3">
-        <v>2918300</v>
+        <v>2877900</v>
       </c>
       <c r="J23" s="3">
-        <v>2443100</v>
+        <v>2409300</v>
       </c>
       <c r="K23" s="3">
         <v>608500</v>
@@ -1367,25 +1367,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>696100</v>
+        <v>686500</v>
       </c>
       <c r="E24" s="3">
-        <v>435300</v>
+        <v>429200</v>
       </c>
       <c r="F24" s="3">
-        <v>88700</v>
+        <v>87500</v>
       </c>
       <c r="G24" s="3">
-        <v>143400</v>
+        <v>141400</v>
       </c>
       <c r="H24" s="3">
-        <v>557200</v>
+        <v>549500</v>
       </c>
       <c r="I24" s="3">
-        <v>442700</v>
+        <v>436500</v>
       </c>
       <c r="J24" s="3">
-        <v>528400</v>
+        <v>521100</v>
       </c>
       <c r="K24" s="3">
         <v>255900</v>
@@ -1457,25 +1457,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>2267200</v>
+        <v>2235800</v>
       </c>
       <c r="E26" s="3">
-        <v>580100</v>
+        <v>572100</v>
       </c>
       <c r="F26" s="3">
-        <v>1512000</v>
+        <v>1491000</v>
       </c>
       <c r="G26" s="3">
-        <v>3630700</v>
+        <v>3580400</v>
       </c>
       <c r="H26" s="3">
-        <v>3275900</v>
+        <v>3230600</v>
       </c>
       <c r="I26" s="3">
-        <v>2475600</v>
+        <v>2441300</v>
       </c>
       <c r="J26" s="3">
-        <v>1914700</v>
+        <v>1888200</v>
       </c>
       <c r="K26" s="3">
         <v>352600</v>
@@ -1502,25 +1502,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>2090600</v>
+        <v>2061700</v>
       </c>
       <c r="E27" s="3">
-        <v>473700</v>
+        <v>467100</v>
       </c>
       <c r="F27" s="3">
-        <v>1341300</v>
+        <v>1322700</v>
       </c>
       <c r="G27" s="3">
-        <v>3293700</v>
+        <v>3248100</v>
       </c>
       <c r="H27" s="3">
-        <v>2938200</v>
+        <v>2897500</v>
       </c>
       <c r="I27" s="3">
-        <v>2491900</v>
+        <v>2457400</v>
       </c>
       <c r="J27" s="3">
-        <v>1620600</v>
+        <v>1598200</v>
       </c>
       <c r="K27" s="3">
         <v>90100</v>
@@ -1607,10 +1607,10 @@
         <v>0</v>
       </c>
       <c r="I29" s="3">
-        <v>123400</v>
+        <v>121700</v>
       </c>
       <c r="J29" s="3">
-        <v>594100</v>
+        <v>585900</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
@@ -1727,25 +1727,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-1877000</v>
+        <v>-1851100</v>
       </c>
       <c r="E32" s="3">
-        <v>-1022800</v>
+        <v>-1008600</v>
       </c>
       <c r="F32" s="3">
-        <v>-1030900</v>
+        <v>-1016600</v>
       </c>
       <c r="G32" s="3">
-        <v>-1131400</v>
+        <v>-1115700</v>
       </c>
       <c r="H32" s="3">
-        <v>-1281400</v>
+        <v>-1263700</v>
       </c>
       <c r="I32" s="3">
-        <v>-985800</v>
+        <v>-972200</v>
       </c>
       <c r="J32" s="3">
-        <v>-1547400</v>
+        <v>-1526000</v>
       </c>
       <c r="K32" s="3">
         <v>-143200</v>
@@ -1772,25 +1772,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>2090600</v>
+        <v>2061700</v>
       </c>
       <c r="E33" s="3">
-        <v>473700</v>
+        <v>467100</v>
       </c>
       <c r="F33" s="3">
-        <v>1341300</v>
+        <v>1322700</v>
       </c>
       <c r="G33" s="3">
-        <v>3293700</v>
+        <v>3248100</v>
       </c>
       <c r="H33" s="3">
-        <v>2938200</v>
+        <v>2897500</v>
       </c>
       <c r="I33" s="3">
-        <v>2615300</v>
+        <v>2579100</v>
       </c>
       <c r="J33" s="3">
-        <v>2214800</v>
+        <v>2184100</v>
       </c>
       <c r="K33" s="3">
         <v>90100</v>
@@ -1862,25 +1862,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>2090600</v>
+        <v>2061700</v>
       </c>
       <c r="E35" s="3">
-        <v>473700</v>
+        <v>467100</v>
       </c>
       <c r="F35" s="3">
-        <v>1341300</v>
+        <v>1322700</v>
       </c>
       <c r="G35" s="3">
-        <v>3293700</v>
+        <v>3248100</v>
       </c>
       <c r="H35" s="3">
-        <v>2938200</v>
+        <v>2897500</v>
       </c>
       <c r="I35" s="3">
-        <v>2615300</v>
+        <v>2579100</v>
       </c>
       <c r="J35" s="3">
-        <v>2214800</v>
+        <v>2184100</v>
       </c>
       <c r="K35" s="3">
         <v>90100</v>
@@ -1995,25 +1995,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>2718000</v>
+        <v>2680400</v>
       </c>
       <c r="E41" s="3">
-        <v>458200</v>
+        <v>451800</v>
       </c>
       <c r="F41" s="3">
-        <v>497300</v>
+        <v>490500</v>
       </c>
       <c r="G41" s="3">
-        <v>1130700</v>
+        <v>1115000</v>
       </c>
       <c r="H41" s="3">
-        <v>992500</v>
+        <v>978700</v>
       </c>
       <c r="I41" s="3">
-        <v>329600</v>
+        <v>325000</v>
       </c>
       <c r="J41" s="3">
-        <v>804800</v>
+        <v>793600</v>
       </c>
       <c r="K41" s="3">
         <v>738600</v>
@@ -2049,13 +2049,13 @@
         <v>8</v>
       </c>
       <c r="G42" s="3">
-        <v>138900</v>
+        <v>137000</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>8</v>
       </c>
       <c r="I42" s="3">
-        <v>529900</v>
+        <v>522500</v>
       </c>
       <c r="J42" s="3" t="s">
         <v>8</v>
@@ -2085,25 +2085,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>3222000</v>
+        <v>3177400</v>
       </c>
       <c r="E43" s="3">
-        <v>2792600</v>
+        <v>2754000</v>
       </c>
       <c r="F43" s="3">
-        <v>3333600</v>
+        <v>3287400</v>
       </c>
       <c r="G43" s="3">
-        <v>1695200</v>
+        <v>1671800</v>
       </c>
       <c r="H43" s="3">
-        <v>1902900</v>
+        <v>1876600</v>
       </c>
       <c r="I43" s="3">
-        <v>1990800</v>
+        <v>1963300</v>
       </c>
       <c r="J43" s="3">
-        <v>1863700</v>
+        <v>1837900</v>
       </c>
       <c r="K43" s="3">
         <v>1508500</v>
@@ -2130,25 +2130,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>725700</v>
+        <v>715600</v>
       </c>
       <c r="E44" s="3">
-        <v>691700</v>
+        <v>682100</v>
       </c>
       <c r="F44" s="3">
-        <v>535000</v>
+        <v>527600</v>
       </c>
       <c r="G44" s="3">
-        <v>464800</v>
+        <v>458400</v>
       </c>
       <c r="H44" s="3">
-        <v>334000</v>
+        <v>329400</v>
       </c>
       <c r="I44" s="3">
-        <v>318500</v>
+        <v>314100</v>
       </c>
       <c r="J44" s="3">
-        <v>279300</v>
+        <v>275500</v>
       </c>
       <c r="K44" s="3">
         <v>267500</v>
@@ -2175,25 +2175,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1738100</v>
+        <v>1714000</v>
       </c>
       <c r="E45" s="3">
-        <v>1475800</v>
+        <v>1455300</v>
       </c>
       <c r="F45" s="3">
-        <v>1119600</v>
+        <v>1104100</v>
       </c>
       <c r="G45" s="3">
-        <v>413800</v>
+        <v>408100</v>
       </c>
       <c r="H45" s="3">
-        <v>2424600</v>
+        <v>2391100</v>
       </c>
       <c r="I45" s="3">
-        <v>625900</v>
+        <v>617300</v>
       </c>
       <c r="J45" s="3">
-        <v>510600</v>
+        <v>503600</v>
       </c>
       <c r="K45" s="3">
         <v>3362400</v>
@@ -2220,25 +2220,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>8403800</v>
+        <v>8287500</v>
       </c>
       <c r="E46" s="3">
-        <v>5418300</v>
+        <v>5343300</v>
       </c>
       <c r="F46" s="3">
-        <v>5485500</v>
+        <v>5409600</v>
       </c>
       <c r="G46" s="3">
-        <v>3843500</v>
+        <v>3790300</v>
       </c>
       <c r="H46" s="3">
-        <v>5654000</v>
+        <v>5575700</v>
       </c>
       <c r="I46" s="3">
-        <v>3794700</v>
+        <v>3742200</v>
       </c>
       <c r="J46" s="3">
-        <v>3458500</v>
+        <v>3410600</v>
       </c>
       <c r="K46" s="3">
         <v>5877100</v>
@@ -2265,25 +2265,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>9632000</v>
+        <v>9498700</v>
       </c>
       <c r="E47" s="3">
-        <v>8709000</v>
+        <v>8588400</v>
       </c>
       <c r="F47" s="3">
-        <v>6597700</v>
+        <v>6506400</v>
       </c>
       <c r="G47" s="3">
-        <v>6078900</v>
+        <v>5994800</v>
       </c>
       <c r="H47" s="3">
-        <v>5867600</v>
+        <v>5786400</v>
       </c>
       <c r="I47" s="3">
-        <v>6265200</v>
+        <v>6178400</v>
       </c>
       <c r="J47" s="3">
-        <v>5434500</v>
+        <v>5359300</v>
       </c>
       <c r="K47" s="3">
         <v>4843300</v>
@@ -2310,25 +2310,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>59539700</v>
+        <v>58715500</v>
       </c>
       <c r="E48" s="3">
-        <v>56118900</v>
+        <v>55342000</v>
       </c>
       <c r="F48" s="3">
-        <v>51863800</v>
+        <v>51145800</v>
       </c>
       <c r="G48" s="3">
-        <v>51563000</v>
+        <v>50849200</v>
       </c>
       <c r="H48" s="3">
-        <v>48395700</v>
+        <v>47725800</v>
       </c>
       <c r="I48" s="3">
-        <v>49145100</v>
+        <v>48464700</v>
       </c>
       <c r="J48" s="3">
-        <v>42327100</v>
+        <v>41741200</v>
       </c>
       <c r="K48" s="3">
         <v>39603900</v>
@@ -2355,25 +2355,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>9261000</v>
+        <v>9132800</v>
       </c>
       <c r="E49" s="3">
-        <v>9490800</v>
+        <v>9359500</v>
       </c>
       <c r="F49" s="3">
-        <v>9298000</v>
+        <v>9169300</v>
       </c>
       <c r="G49" s="3">
-        <v>9369700</v>
+        <v>9239900</v>
       </c>
       <c r="H49" s="3">
-        <v>9523400</v>
+        <v>9391500</v>
       </c>
       <c r="I49" s="3">
-        <v>10477400</v>
+        <v>10332400</v>
       </c>
       <c r="J49" s="3">
-        <v>9668900</v>
+        <v>9535100</v>
       </c>
       <c r="K49" s="3">
         <v>10147600</v>
@@ -2490,25 +2490,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>5562400</v>
+        <v>5485400</v>
       </c>
       <c r="E52" s="3">
-        <v>4765000</v>
+        <v>4699000</v>
       </c>
       <c r="F52" s="3">
-        <v>3771100</v>
+        <v>3718900</v>
       </c>
       <c r="G52" s="3">
-        <v>3265600</v>
+        <v>3220400</v>
       </c>
       <c r="H52" s="3">
-        <v>3925500</v>
+        <v>3871200</v>
       </c>
       <c r="I52" s="3">
-        <v>3418600</v>
+        <v>3371200</v>
       </c>
       <c r="J52" s="3">
-        <v>2738700</v>
+        <v>2700800</v>
       </c>
       <c r="K52" s="3">
         <v>3542000</v>
@@ -2580,25 +2580,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>92398900</v>
+        <v>91119800</v>
       </c>
       <c r="E54" s="3">
-        <v>84502000</v>
+        <v>83332200</v>
       </c>
       <c r="F54" s="3">
-        <v>77016100</v>
+        <v>75949900</v>
       </c>
       <c r="G54" s="3">
-        <v>74120700</v>
+        <v>73094600</v>
       </c>
       <c r="H54" s="3">
-        <v>73366200</v>
+        <v>72350600</v>
       </c>
       <c r="I54" s="3">
-        <v>73100900</v>
+        <v>72088900</v>
       </c>
       <c r="J54" s="3">
-        <v>63627800</v>
+        <v>62747000</v>
       </c>
       <c r="K54" s="3">
         <v>64014000</v>
@@ -2663,25 +2663,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>3661000</v>
+        <v>3610300</v>
       </c>
       <c r="E57" s="3">
-        <v>4077000</v>
+        <v>4020600</v>
       </c>
       <c r="F57" s="3">
-        <v>3091200</v>
+        <v>3048400</v>
       </c>
       <c r="G57" s="3">
-        <v>2259100</v>
+        <v>2227800</v>
       </c>
       <c r="H57" s="3">
-        <v>2758600</v>
+        <v>2720500</v>
       </c>
       <c r="I57" s="3">
-        <v>2878400</v>
+        <v>2838500</v>
       </c>
       <c r="J57" s="3">
-        <v>2712100</v>
+        <v>2674500</v>
       </c>
       <c r="K57" s="3">
         <v>2006500</v>
@@ -2708,25 +2708,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2171200</v>
+        <v>2141100</v>
       </c>
       <c r="E58" s="3">
-        <v>6030200</v>
+        <v>5946700</v>
       </c>
       <c r="F58" s="3">
-        <v>4793100</v>
+        <v>4726700</v>
       </c>
       <c r="G58" s="3">
-        <v>4543300</v>
+        <v>4480400</v>
       </c>
       <c r="H58" s="3">
-        <v>5176600</v>
+        <v>5105000</v>
       </c>
       <c r="I58" s="3">
-        <v>4599500</v>
+        <v>4535800</v>
       </c>
       <c r="J58" s="3">
-        <v>3420800</v>
+        <v>3373400</v>
       </c>
       <c r="K58" s="3">
         <v>1899000</v>
@@ -2753,25 +2753,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2900500</v>
+        <v>2860400</v>
       </c>
       <c r="E59" s="3">
-        <v>2386900</v>
+        <v>2353900</v>
       </c>
       <c r="F59" s="3">
-        <v>1752900</v>
+        <v>1728600</v>
       </c>
       <c r="G59" s="3">
-        <v>2055900</v>
+        <v>2027400</v>
       </c>
       <c r="H59" s="3">
-        <v>1597000</v>
+        <v>1574900</v>
       </c>
       <c r="I59" s="3">
-        <v>2089100</v>
+        <v>2060200</v>
       </c>
       <c r="J59" s="3">
-        <v>1166100</v>
+        <v>1150000</v>
       </c>
       <c r="K59" s="3">
         <v>1677900</v>
@@ -2798,25 +2798,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>8732600</v>
+        <v>8611800</v>
       </c>
       <c r="E60" s="3">
-        <v>12494100</v>
+        <v>12321100</v>
       </c>
       <c r="F60" s="3">
-        <v>9637200</v>
+        <v>9503800</v>
       </c>
       <c r="G60" s="3">
-        <v>8858300</v>
+        <v>8735600</v>
       </c>
       <c r="H60" s="3">
-        <v>9532200</v>
+        <v>9400300</v>
       </c>
       <c r="I60" s="3">
-        <v>9567000</v>
+        <v>9434500</v>
       </c>
       <c r="J60" s="3">
-        <v>7299000</v>
+        <v>7198000</v>
       </c>
       <c r="K60" s="3">
         <v>5583400</v>
@@ -2843,25 +2843,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>44533800</v>
+        <v>43917300</v>
       </c>
       <c r="E61" s="3">
-        <v>37053000</v>
+        <v>36540000</v>
       </c>
       <c r="F61" s="3">
-        <v>34200500</v>
+        <v>33727000</v>
       </c>
       <c r="G61" s="3">
-        <v>32080300</v>
+        <v>31636200</v>
       </c>
       <c r="H61" s="3">
-        <v>31698200</v>
+        <v>31259400</v>
       </c>
       <c r="I61" s="3">
-        <v>32528100</v>
+        <v>32077800</v>
       </c>
       <c r="J61" s="3">
-        <v>28733400</v>
+        <v>28335600</v>
       </c>
       <c r="K61" s="3">
         <v>30711100</v>
@@ -2888,25 +2888,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>10306000</v>
+        <v>10163300</v>
       </c>
       <c r="E62" s="3">
-        <v>9743600</v>
+        <v>9608700</v>
       </c>
       <c r="F62" s="3">
-        <v>8499100</v>
+        <v>8381500</v>
       </c>
       <c r="G62" s="3">
-        <v>8445900</v>
+        <v>8329000</v>
       </c>
       <c r="H62" s="3">
-        <v>8194700</v>
+        <v>8081200</v>
       </c>
       <c r="I62" s="3">
-        <v>8102300</v>
+        <v>7990100</v>
       </c>
       <c r="J62" s="3">
-        <v>7723200</v>
+        <v>7616300</v>
       </c>
       <c r="K62" s="3">
         <v>8829500</v>
@@ -3068,25 +3068,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>70559500</v>
+        <v>69582700</v>
       </c>
       <c r="E66" s="3">
-        <v>59383800</v>
+        <v>58561700</v>
       </c>
       <c r="F66" s="3">
-        <v>52429100</v>
+        <v>51703300</v>
       </c>
       <c r="G66" s="3">
-        <v>50917900</v>
+        <v>50213000</v>
       </c>
       <c r="H66" s="3">
-        <v>50632600</v>
+        <v>49931700</v>
       </c>
       <c r="I66" s="3">
-        <v>51420400</v>
+        <v>50708600</v>
       </c>
       <c r="J66" s="3">
-        <v>45124200</v>
+        <v>44499500</v>
       </c>
       <c r="K66" s="3">
         <v>46378900</v>
@@ -3222,25 +3222,25 @@
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>1846700</v>
+        <v>1821200</v>
       </c>
       <c r="E70" s="3">
-        <v>1846700</v>
+        <v>1821200</v>
       </c>
       <c r="F70" s="3">
-        <v>2576900</v>
+        <v>2541200</v>
       </c>
       <c r="G70" s="3">
-        <v>2941200</v>
+        <v>2900500</v>
       </c>
       <c r="H70" s="3">
-        <v>2941200</v>
+        <v>2900500</v>
       </c>
       <c r="I70" s="3">
-        <v>2941200</v>
+        <v>2900500</v>
       </c>
       <c r="J70" s="3">
-        <v>2941200</v>
+        <v>2900500</v>
       </c>
       <c r="K70" s="3">
         <v>2893500</v>
@@ -3312,25 +3312,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-2214800</v>
+        <v>-2184100</v>
       </c>
       <c r="E72" s="3">
-        <v>605200</v>
+        <v>596900</v>
       </c>
       <c r="F72" s="3">
-        <v>2788200</v>
+        <v>2749600</v>
       </c>
       <c r="G72" s="3">
-        <v>3966200</v>
+        <v>3911300</v>
       </c>
       <c r="H72" s="3">
-        <v>2922700</v>
+        <v>2882200</v>
       </c>
       <c r="I72" s="3">
-        <v>2049200</v>
+        <v>2020900</v>
       </c>
       <c r="J72" s="3">
-        <v>1199400</v>
+        <v>1182800</v>
       </c>
       <c r="K72" s="3">
         <v>827300</v>
@@ -3492,25 +3492,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>19992700</v>
+        <v>19715800</v>
       </c>
       <c r="E76" s="3">
-        <v>23271600</v>
+        <v>22949400</v>
       </c>
       <c r="F76" s="3">
-        <v>22010000</v>
+        <v>21705400</v>
       </c>
       <c r="G76" s="3">
-        <v>20261600</v>
+        <v>19981100</v>
       </c>
       <c r="H76" s="3">
-        <v>19792300</v>
+        <v>19518300</v>
       </c>
       <c r="I76" s="3">
-        <v>18739300</v>
+        <v>18479900</v>
       </c>
       <c r="J76" s="3">
-        <v>15562400</v>
+        <v>15346900</v>
       </c>
       <c r="K76" s="3">
         <v>14741600</v>
@@ -3632,25 +3632,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>2090600</v>
+        <v>2061700</v>
       </c>
       <c r="E81" s="3">
-        <v>473700</v>
+        <v>467100</v>
       </c>
       <c r="F81" s="3">
-        <v>1341300</v>
+        <v>1322700</v>
       </c>
       <c r="G81" s="3">
-        <v>3293700</v>
+        <v>3248100</v>
       </c>
       <c r="H81" s="3">
-        <v>2938200</v>
+        <v>2897500</v>
       </c>
       <c r="I81" s="3">
-        <v>2615300</v>
+        <v>2579100</v>
       </c>
       <c r="J81" s="3">
-        <v>2214800</v>
+        <v>2184100</v>
       </c>
       <c r="K81" s="3">
         <v>90100</v>
@@ -3696,25 +3696,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>2052900</v>
+        <v>2024500</v>
       </c>
       <c r="E83" s="3">
-        <v>1909600</v>
+        <v>1883100</v>
       </c>
       <c r="F83" s="3">
-        <v>1863700</v>
+        <v>1837900</v>
       </c>
       <c r="G83" s="3">
-        <v>1914000</v>
+        <v>1887500</v>
       </c>
       <c r="H83" s="3">
-        <v>1820900</v>
+        <v>1795700</v>
       </c>
       <c r="I83" s="3">
-        <v>1736600</v>
+        <v>1712600</v>
       </c>
       <c r="J83" s="3">
-        <v>1518600</v>
+        <v>1497600</v>
       </c>
       <c r="K83" s="3">
         <v>1409700</v>
@@ -3966,25 +3966,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>5371000</v>
+        <v>5296600</v>
       </c>
       <c r="E89" s="3">
-        <v>4711100</v>
+        <v>4645800</v>
       </c>
       <c r="F89" s="3">
-        <v>5091600</v>
+        <v>5021200</v>
       </c>
       <c r="G89" s="3">
-        <v>5215800</v>
+        <v>5143600</v>
       </c>
       <c r="H89" s="3">
-        <v>5233500</v>
+        <v>5161100</v>
       </c>
       <c r="I89" s="3">
-        <v>4844100</v>
+        <v>4777000</v>
       </c>
       <c r="J89" s="3">
-        <v>3864900</v>
+        <v>3811400</v>
       </c>
       <c r="K89" s="3">
         <v>3685200</v>
@@ -4030,25 +4030,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-6022000</v>
+        <v>-5938700</v>
       </c>
       <c r="E91" s="3">
-        <v>-4971200</v>
+        <v>-4902400</v>
       </c>
       <c r="F91" s="3">
-        <v>-4377800</v>
+        <v>-4317200</v>
       </c>
       <c r="G91" s="3">
-        <v>-6011700</v>
+        <v>-5928500</v>
       </c>
       <c r="H91" s="3">
-        <v>-6046400</v>
+        <v>-5962700</v>
       </c>
       <c r="I91" s="3">
-        <v>-7326300</v>
+        <v>-7224900</v>
       </c>
       <c r="J91" s="3">
-        <v>-5563900</v>
+        <v>-5486800</v>
       </c>
       <c r="K91" s="3">
         <v>-3854600</v>
@@ -4165,25 +4165,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-9080000</v>
+        <v>-8954300</v>
       </c>
       <c r="E94" s="3">
-        <v>-5179600</v>
+        <v>-5107900</v>
       </c>
       <c r="F94" s="3">
-        <v>-5699100</v>
+        <v>-5620200</v>
       </c>
       <c r="G94" s="3">
-        <v>-4472400</v>
+        <v>-4410500</v>
       </c>
       <c r="H94" s="3">
-        <v>-5078300</v>
+        <v>-5008000</v>
       </c>
       <c r="I94" s="3">
-        <v>-7403900</v>
+        <v>-7301400</v>
       </c>
       <c r="J94" s="3">
-        <v>-2733500</v>
+        <v>-2695700</v>
       </c>
       <c r="K94" s="3">
         <v>-13655400</v>
@@ -4229,25 +4229,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-2127600</v>
+        <v>-2098100</v>
       </c>
       <c r="E96" s="3">
-        <v>-2437200</v>
+        <v>-2403500</v>
       </c>
       <c r="F96" s="3">
-        <v>-2555400</v>
+        <v>-2520100</v>
       </c>
       <c r="G96" s="3">
-        <v>-2324900</v>
+        <v>-2292700</v>
       </c>
       <c r="H96" s="3">
-        <v>-1446900</v>
+        <v>-1426900</v>
       </c>
       <c r="I96" s="3">
-        <v>-1277700</v>
+        <v>-1260000</v>
       </c>
       <c r="J96" s="3">
-        <v>-1104100</v>
+        <v>-1088800</v>
       </c>
       <c r="K96" s="3">
         <v>-1116700</v>
@@ -4409,25 +4409,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>5980600</v>
+        <v>5897900</v>
       </c>
       <c r="E100" s="3">
-        <v>359900</v>
+        <v>354900</v>
       </c>
       <c r="F100" s="3">
-        <v>-65000</v>
+        <v>-64100</v>
       </c>
       <c r="G100" s="3">
-        <v>-591200</v>
+        <v>-583000</v>
       </c>
       <c r="H100" s="3">
-        <v>512100</v>
+        <v>505000</v>
       </c>
       <c r="I100" s="3">
-        <v>2030700</v>
+        <v>2002600</v>
       </c>
       <c r="J100" s="3">
-        <v>-1048600</v>
+        <v>-1034100</v>
       </c>
       <c r="K100" s="3">
         <v>10183200</v>
@@ -4454,25 +4454,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-11800</v>
+        <v>-11700</v>
       </c>
       <c r="E101" s="3">
-        <v>69500</v>
+        <v>68500</v>
       </c>
       <c r="F101" s="3">
-        <v>39200</v>
+        <v>38600</v>
       </c>
       <c r="G101" s="3">
-        <v>-14000</v>
+        <v>-13800</v>
       </c>
       <c r="H101" s="3">
         <v>-4400</v>
       </c>
       <c r="I101" s="3">
-        <v>53900</v>
+        <v>53200</v>
       </c>
       <c r="J101" s="3">
-        <v>-28800</v>
+        <v>-28400</v>
       </c>
       <c r="K101" s="3">
         <v>-92300</v>
@@ -4499,25 +4499,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>2259800</v>
+        <v>2228500</v>
       </c>
       <c r="E102" s="3">
-        <v>-39200</v>
+        <v>-38600</v>
       </c>
       <c r="F102" s="3">
-        <v>-633300</v>
+        <v>-624500</v>
       </c>
       <c r="G102" s="3">
-        <v>138200</v>
+        <v>136300</v>
       </c>
       <c r="H102" s="3">
-        <v>662900</v>
+        <v>653700</v>
       </c>
       <c r="I102" s="3">
-        <v>-475200</v>
+        <v>-468600</v>
       </c>
       <c r="J102" s="3">
-        <v>53900</v>
+        <v>53200</v>
       </c>
       <c r="K102" s="3">
         <v>120700</v>

--- a/AAII_Financials/Yearly/TRP_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/TRP_YR_FIN.xlsx
@@ -728,25 +728,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>11612100</v>
+        <v>11729200</v>
       </c>
       <c r="E8" s="3">
-        <v>10914600</v>
+        <v>11024700</v>
       </c>
       <c r="F8" s="3">
-        <v>9755900</v>
+        <v>9854300</v>
       </c>
       <c r="G8" s="3">
-        <v>9473200</v>
+        <v>9568700</v>
       </c>
       <c r="H8" s="3">
-        <v>9659700</v>
+        <v>9757100</v>
       </c>
       <c r="I8" s="3">
-        <v>9968700</v>
+        <v>10069200</v>
       </c>
       <c r="J8" s="3">
-        <v>9801100</v>
+        <v>9899900</v>
       </c>
       <c r="K8" s="3">
         <v>9121800</v>
@@ -773,25 +773,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>3561500</v>
+        <v>3597400</v>
       </c>
       <c r="E9" s="3">
-        <v>3594200</v>
+        <v>3630500</v>
       </c>
       <c r="F9" s="3">
-        <v>2986500</v>
+        <v>3016600</v>
       </c>
       <c r="G9" s="3">
-        <v>2826100</v>
+        <v>2854600</v>
       </c>
       <c r="H9" s="3">
-        <v>2848700</v>
+        <v>2877500</v>
       </c>
       <c r="I9" s="3">
-        <v>2617000</v>
+        <v>2643400</v>
       </c>
       <c r="J9" s="3">
-        <v>2846500</v>
+        <v>2875200</v>
       </c>
       <c r="K9" s="3">
         <v>2807000</v>
@@ -818,25 +818,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>8050600</v>
+        <v>8131800</v>
       </c>
       <c r="E10" s="3">
-        <v>7320400</v>
+        <v>7394200</v>
       </c>
       <c r="F10" s="3">
-        <v>6769500</v>
+        <v>6837700</v>
       </c>
       <c r="G10" s="3">
-        <v>6647000</v>
+        <v>6714100</v>
       </c>
       <c r="H10" s="3">
-        <v>6811000</v>
+        <v>6879700</v>
       </c>
       <c r="I10" s="3">
-        <v>7351700</v>
+        <v>7425900</v>
       </c>
       <c r="J10" s="3">
-        <v>6954600</v>
+        <v>7024700</v>
       </c>
       <c r="K10" s="3">
         <v>6314800</v>
@@ -972,13 +972,13 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>1553700</v>
+        <v>1569400</v>
       </c>
       <c r="E14" s="3">
-        <v>2551400</v>
+        <v>2577100</v>
       </c>
       <c r="F14" s="3">
-        <v>2022300</v>
+        <v>2042700</v>
       </c>
       <c r="G14" s="3">
         <v>0</v>
@@ -987,10 +987,10 @@
         <v>0</v>
       </c>
       <c r="I14" s="3">
-        <v>583700</v>
+        <v>589600</v>
       </c>
       <c r="J14" s="3">
-        <v>916100</v>
+        <v>925300</v>
       </c>
       <c r="K14" s="3">
         <v>1088300</v>
@@ -1017,25 +1017,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>2024500</v>
+        <v>2044900</v>
       </c>
       <c r="E15" s="3">
-        <v>1883100</v>
+        <v>1902100</v>
       </c>
       <c r="F15" s="3">
-        <v>1837900</v>
+        <v>1856500</v>
       </c>
       <c r="G15" s="3">
-        <v>1887500</v>
+        <v>1906500</v>
       </c>
       <c r="H15" s="3">
-        <v>1795700</v>
+        <v>1813800</v>
       </c>
       <c r="I15" s="3">
-        <v>1712600</v>
+        <v>1729900</v>
       </c>
       <c r="J15" s="3">
-        <v>1497600</v>
+        <v>1512700</v>
       </c>
       <c r="K15" s="3">
         <v>1409700</v>
@@ -1078,25 +1078,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>8170100</v>
+        <v>8252500</v>
       </c>
       <c r="E17" s="3">
-        <v>9035900</v>
+        <v>9127000</v>
       </c>
       <c r="F17" s="3">
-        <v>7474200</v>
+        <v>7549500</v>
       </c>
       <c r="G17" s="3">
-        <v>5243400</v>
+        <v>5296300</v>
       </c>
       <c r="H17" s="3">
-        <v>5443100</v>
+        <v>5498000</v>
       </c>
       <c r="I17" s="3">
-        <v>6412400</v>
+        <v>6477000</v>
       </c>
       <c r="J17" s="3">
-        <v>7410800</v>
+        <v>7485500</v>
       </c>
       <c r="K17" s="3">
         <v>7287500</v>
@@ -1123,25 +1123,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>3441900</v>
+        <v>3476600</v>
       </c>
       <c r="E18" s="3">
-        <v>1878700</v>
+        <v>1897700</v>
       </c>
       <c r="F18" s="3">
-        <v>2281700</v>
+        <v>2304800</v>
       </c>
       <c r="G18" s="3">
-        <v>4229700</v>
+        <v>4272400</v>
       </c>
       <c r="H18" s="3">
-        <v>4216600</v>
+        <v>4259100</v>
       </c>
       <c r="I18" s="3">
-        <v>3556300</v>
+        <v>3592200</v>
       </c>
       <c r="J18" s="3">
-        <v>2390300</v>
+        <v>2414400</v>
       </c>
       <c r="K18" s="3">
         <v>1834200</v>
@@ -1187,25 +1187,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>1851100</v>
+        <v>1869700</v>
       </c>
       <c r="E20" s="3">
-        <v>1008600</v>
+        <v>1018800</v>
       </c>
       <c r="F20" s="3">
-        <v>1016600</v>
+        <v>1026900</v>
       </c>
       <c r="G20" s="3">
-        <v>1115700</v>
+        <v>1127000</v>
       </c>
       <c r="H20" s="3">
-        <v>1263700</v>
+        <v>1276400</v>
       </c>
       <c r="I20" s="3">
-        <v>972200</v>
+        <v>982000</v>
       </c>
       <c r="J20" s="3">
-        <v>1526000</v>
+        <v>1541400</v>
       </c>
       <c r="K20" s="3">
         <v>143200</v>
@@ -1232,25 +1232,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>7312300</v>
+        <v>7392000</v>
       </c>
       <c r="E21" s="3">
-        <v>4765700</v>
+        <v>4819300</v>
       </c>
       <c r="F21" s="3">
-        <v>5131600</v>
+        <v>5188800</v>
       </c>
       <c r="G21" s="3">
-        <v>7228100</v>
+        <v>7306600</v>
       </c>
       <c r="H21" s="3">
-        <v>7271400</v>
+        <v>7350000</v>
       </c>
       <c r="I21" s="3">
-        <v>6236700</v>
+        <v>6304700</v>
       </c>
       <c r="J21" s="3">
-        <v>5410100</v>
+        <v>5469100</v>
       </c>
       <c r="K21" s="3">
         <v>3395100</v>
@@ -1277,25 +1277,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>2370700</v>
+        <v>2394600</v>
       </c>
       <c r="E22" s="3">
-        <v>1886000</v>
+        <v>1905100</v>
       </c>
       <c r="F22" s="3">
-        <v>1719900</v>
+        <v>1737200</v>
       </c>
       <c r="G22" s="3">
-        <v>1623700</v>
+        <v>1640100</v>
       </c>
       <c r="H22" s="3">
-        <v>1700200</v>
+        <v>1717300</v>
       </c>
       <c r="I22" s="3">
-        <v>1650600</v>
+        <v>1667300</v>
       </c>
       <c r="J22" s="3">
-        <v>1507100</v>
+        <v>1522300</v>
       </c>
       <c r="K22" s="3">
         <v>1369000</v>
@@ -1322,25 +1322,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>2922300</v>
+        <v>2951800</v>
       </c>
       <c r="E23" s="3">
-        <v>1001300</v>
+        <v>1011400</v>
       </c>
       <c r="F23" s="3">
-        <v>1578500</v>
+        <v>1594400</v>
       </c>
       <c r="G23" s="3">
-        <v>3721800</v>
+        <v>3759300</v>
       </c>
       <c r="H23" s="3">
-        <v>3780100</v>
+        <v>3818200</v>
       </c>
       <c r="I23" s="3">
-        <v>2877900</v>
+        <v>2906900</v>
       </c>
       <c r="J23" s="3">
-        <v>2409300</v>
+        <v>2433600</v>
       </c>
       <c r="K23" s="3">
         <v>608500</v>
@@ -1367,25 +1367,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>686500</v>
+        <v>693400</v>
       </c>
       <c r="E24" s="3">
-        <v>429200</v>
+        <v>433600</v>
       </c>
       <c r="F24" s="3">
-        <v>87500</v>
+        <v>88300</v>
       </c>
       <c r="G24" s="3">
-        <v>141400</v>
+        <v>142800</v>
       </c>
       <c r="H24" s="3">
-        <v>549500</v>
+        <v>555000</v>
       </c>
       <c r="I24" s="3">
-        <v>436500</v>
+        <v>440900</v>
       </c>
       <c r="J24" s="3">
-        <v>521100</v>
+        <v>526300</v>
       </c>
       <c r="K24" s="3">
         <v>255900</v>
@@ -1457,25 +1457,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>2235800</v>
+        <v>2258400</v>
       </c>
       <c r="E26" s="3">
-        <v>572100</v>
+        <v>577800</v>
       </c>
       <c r="F26" s="3">
-        <v>1491000</v>
+        <v>1506100</v>
       </c>
       <c r="G26" s="3">
-        <v>3580400</v>
+        <v>3616500</v>
       </c>
       <c r="H26" s="3">
-        <v>3230600</v>
+        <v>3263200</v>
       </c>
       <c r="I26" s="3">
-        <v>2441300</v>
+        <v>2466000</v>
       </c>
       <c r="J26" s="3">
-        <v>1888200</v>
+        <v>1907300</v>
       </c>
       <c r="K26" s="3">
         <v>352600</v>
@@ -1502,25 +1502,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>2061700</v>
+        <v>2082500</v>
       </c>
       <c r="E27" s="3">
-        <v>467100</v>
+        <v>471800</v>
       </c>
       <c r="F27" s="3">
-        <v>1322700</v>
+        <v>1336000</v>
       </c>
       <c r="G27" s="3">
-        <v>3248100</v>
+        <v>3280800</v>
       </c>
       <c r="H27" s="3">
-        <v>2897500</v>
+        <v>2926800</v>
       </c>
       <c r="I27" s="3">
-        <v>2457400</v>
+        <v>2482200</v>
       </c>
       <c r="J27" s="3">
-        <v>1598200</v>
+        <v>1614300</v>
       </c>
       <c r="K27" s="3">
         <v>90100</v>
@@ -1607,10 +1607,10 @@
         <v>0</v>
       </c>
       <c r="I29" s="3">
-        <v>121700</v>
+        <v>122900</v>
       </c>
       <c r="J29" s="3">
-        <v>585900</v>
+        <v>591800</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
@@ -1727,25 +1727,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-1851100</v>
+        <v>-1869700</v>
       </c>
       <c r="E32" s="3">
-        <v>-1008600</v>
+        <v>-1018800</v>
       </c>
       <c r="F32" s="3">
-        <v>-1016600</v>
+        <v>-1026900</v>
       </c>
       <c r="G32" s="3">
-        <v>-1115700</v>
+        <v>-1127000</v>
       </c>
       <c r="H32" s="3">
-        <v>-1263700</v>
+        <v>-1276400</v>
       </c>
       <c r="I32" s="3">
-        <v>-972200</v>
+        <v>-982000</v>
       </c>
       <c r="J32" s="3">
-        <v>-1526000</v>
+        <v>-1541400</v>
       </c>
       <c r="K32" s="3">
         <v>-143200</v>
@@ -1772,25 +1772,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>2061700</v>
+        <v>2082500</v>
       </c>
       <c r="E33" s="3">
-        <v>467100</v>
+        <v>471800</v>
       </c>
       <c r="F33" s="3">
-        <v>1322700</v>
+        <v>1336000</v>
       </c>
       <c r="G33" s="3">
-        <v>3248100</v>
+        <v>3280800</v>
       </c>
       <c r="H33" s="3">
-        <v>2897500</v>
+        <v>2926800</v>
       </c>
       <c r="I33" s="3">
-        <v>2579100</v>
+        <v>2605100</v>
       </c>
       <c r="J33" s="3">
-        <v>2184100</v>
+        <v>2206100</v>
       </c>
       <c r="K33" s="3">
         <v>90100</v>
@@ -1862,25 +1862,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>2061700</v>
+        <v>2082500</v>
       </c>
       <c r="E35" s="3">
-        <v>467100</v>
+        <v>471800</v>
       </c>
       <c r="F35" s="3">
-        <v>1322700</v>
+        <v>1336000</v>
       </c>
       <c r="G35" s="3">
-        <v>3248100</v>
+        <v>3280800</v>
       </c>
       <c r="H35" s="3">
-        <v>2897500</v>
+        <v>2926800</v>
       </c>
       <c r="I35" s="3">
-        <v>2579100</v>
+        <v>2605100</v>
       </c>
       <c r="J35" s="3">
-        <v>2184100</v>
+        <v>2206100</v>
       </c>
       <c r="K35" s="3">
         <v>90100</v>
@@ -1995,25 +1995,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>2680400</v>
+        <v>2707400</v>
       </c>
       <c r="E41" s="3">
-        <v>451800</v>
+        <v>456400</v>
       </c>
       <c r="F41" s="3">
-        <v>490500</v>
+        <v>495400</v>
       </c>
       <c r="G41" s="3">
-        <v>1115000</v>
+        <v>1126200</v>
       </c>
       <c r="H41" s="3">
-        <v>978700</v>
+        <v>988600</v>
       </c>
       <c r="I41" s="3">
-        <v>325000</v>
+        <v>328300</v>
       </c>
       <c r="J41" s="3">
-        <v>793600</v>
+        <v>801600</v>
       </c>
       <c r="K41" s="3">
         <v>738600</v>
@@ -2049,13 +2049,13 @@
         <v>8</v>
       </c>
       <c r="G42" s="3">
-        <v>137000</v>
+        <v>138400</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>8</v>
       </c>
       <c r="I42" s="3">
-        <v>522500</v>
+        <v>527800</v>
       </c>
       <c r="J42" s="3" t="s">
         <v>8</v>
@@ -2085,25 +2085,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>3177400</v>
+        <v>3209400</v>
       </c>
       <c r="E43" s="3">
-        <v>2754000</v>
+        <v>2781800</v>
       </c>
       <c r="F43" s="3">
-        <v>3287400</v>
+        <v>3320600</v>
       </c>
       <c r="G43" s="3">
-        <v>1671800</v>
+        <v>1688600</v>
       </c>
       <c r="H43" s="3">
-        <v>1876600</v>
+        <v>1895500</v>
       </c>
       <c r="I43" s="3">
-        <v>1963300</v>
+        <v>1983100</v>
       </c>
       <c r="J43" s="3">
-        <v>1837900</v>
+        <v>1856500</v>
       </c>
       <c r="K43" s="3">
         <v>1508500</v>
@@ -2130,25 +2130,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>715600</v>
+        <v>722900</v>
       </c>
       <c r="E44" s="3">
-        <v>682100</v>
+        <v>689000</v>
       </c>
       <c r="F44" s="3">
-        <v>527600</v>
+        <v>532900</v>
       </c>
       <c r="G44" s="3">
-        <v>458400</v>
+        <v>463000</v>
       </c>
       <c r="H44" s="3">
-        <v>329400</v>
+        <v>332700</v>
       </c>
       <c r="I44" s="3">
-        <v>314100</v>
+        <v>317300</v>
       </c>
       <c r="J44" s="3">
-        <v>275500</v>
+        <v>278200</v>
       </c>
       <c r="K44" s="3">
         <v>267500</v>
@@ -2175,25 +2175,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1714000</v>
+        <v>1731300</v>
       </c>
       <c r="E45" s="3">
-        <v>1455300</v>
+        <v>1470000</v>
       </c>
       <c r="F45" s="3">
-        <v>1104100</v>
+        <v>1115200</v>
       </c>
       <c r="G45" s="3">
-        <v>408100</v>
+        <v>412200</v>
       </c>
       <c r="H45" s="3">
-        <v>2391100</v>
+        <v>2415200</v>
       </c>
       <c r="I45" s="3">
-        <v>617300</v>
+        <v>623500</v>
       </c>
       <c r="J45" s="3">
-        <v>503600</v>
+        <v>508700</v>
       </c>
       <c r="K45" s="3">
         <v>3362400</v>
@@ -2220,25 +2220,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>8287500</v>
+        <v>8371000</v>
       </c>
       <c r="E46" s="3">
-        <v>5343300</v>
+        <v>5397200</v>
       </c>
       <c r="F46" s="3">
-        <v>5409600</v>
+        <v>5464100</v>
       </c>
       <c r="G46" s="3">
-        <v>3790300</v>
+        <v>3828500</v>
       </c>
       <c r="H46" s="3">
-        <v>5575700</v>
+        <v>5632000</v>
       </c>
       <c r="I46" s="3">
-        <v>3742200</v>
+        <v>3779900</v>
       </c>
       <c r="J46" s="3">
-        <v>3410600</v>
+        <v>3445000</v>
       </c>
       <c r="K46" s="3">
         <v>5877100</v>
@@ -2265,25 +2265,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>9498700</v>
+        <v>9594500</v>
       </c>
       <c r="E47" s="3">
-        <v>8588400</v>
+        <v>8675100</v>
       </c>
       <c r="F47" s="3">
-        <v>6506400</v>
+        <v>6572000</v>
       </c>
       <c r="G47" s="3">
-        <v>5994800</v>
+        <v>6055200</v>
       </c>
       <c r="H47" s="3">
-        <v>5786400</v>
+        <v>5844700</v>
       </c>
       <c r="I47" s="3">
-        <v>6178400</v>
+        <v>6240700</v>
       </c>
       <c r="J47" s="3">
-        <v>5359300</v>
+        <v>5413400</v>
       </c>
       <c r="K47" s="3">
         <v>4843300</v>
@@ -2310,25 +2310,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>58715500</v>
+        <v>59307600</v>
       </c>
       <c r="E48" s="3">
-        <v>55342000</v>
+        <v>55900200</v>
       </c>
       <c r="F48" s="3">
-        <v>51145800</v>
+        <v>51661700</v>
       </c>
       <c r="G48" s="3">
-        <v>50849200</v>
+        <v>51362100</v>
       </c>
       <c r="H48" s="3">
-        <v>47725800</v>
+        <v>48207100</v>
       </c>
       <c r="I48" s="3">
-        <v>48464700</v>
+        <v>48953500</v>
       </c>
       <c r="J48" s="3">
-        <v>41741200</v>
+        <v>42162200</v>
       </c>
       <c r="K48" s="3">
         <v>39603900</v>
@@ -2355,25 +2355,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>9132800</v>
+        <v>9224900</v>
       </c>
       <c r="E49" s="3">
-        <v>9359500</v>
+        <v>9453900</v>
       </c>
       <c r="F49" s="3">
-        <v>9169300</v>
+        <v>9261700</v>
       </c>
       <c r="G49" s="3">
-        <v>9239900</v>
+        <v>9333100</v>
       </c>
       <c r="H49" s="3">
-        <v>9391500</v>
+        <v>9486200</v>
       </c>
       <c r="I49" s="3">
-        <v>10332400</v>
+        <v>10436600</v>
       </c>
       <c r="J49" s="3">
-        <v>9535100</v>
+        <v>9631300</v>
       </c>
       <c r="K49" s="3">
         <v>10147600</v>
@@ -2490,25 +2490,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>5485400</v>
+        <v>5540700</v>
       </c>
       <c r="E52" s="3">
-        <v>4699000</v>
+        <v>4746400</v>
       </c>
       <c r="F52" s="3">
-        <v>3718900</v>
+        <v>3756400</v>
       </c>
       <c r="G52" s="3">
-        <v>3220400</v>
+        <v>3252900</v>
       </c>
       <c r="H52" s="3">
-        <v>3871200</v>
+        <v>3910200</v>
       </c>
       <c r="I52" s="3">
-        <v>3371200</v>
+        <v>3405200</v>
       </c>
       <c r="J52" s="3">
-        <v>2700800</v>
+        <v>2728000</v>
       </c>
       <c r="K52" s="3">
         <v>3542000</v>
@@ -2580,25 +2580,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>91119800</v>
+        <v>92038800</v>
       </c>
       <c r="E54" s="3">
-        <v>83332200</v>
+        <v>84172700</v>
       </c>
       <c r="F54" s="3">
-        <v>75949900</v>
+        <v>76715900</v>
       </c>
       <c r="G54" s="3">
-        <v>73094600</v>
+        <v>73831800</v>
       </c>
       <c r="H54" s="3">
-        <v>72350600</v>
+        <v>73080300</v>
       </c>
       <c r="I54" s="3">
-        <v>72088900</v>
+        <v>72816000</v>
       </c>
       <c r="J54" s="3">
-        <v>62747000</v>
+        <v>63379800</v>
       </c>
       <c r="K54" s="3">
         <v>64014000</v>
@@ -2663,25 +2663,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>3610300</v>
+        <v>3646700</v>
       </c>
       <c r="E57" s="3">
-        <v>4020600</v>
+        <v>4061100</v>
       </c>
       <c r="F57" s="3">
-        <v>3048400</v>
+        <v>3079100</v>
       </c>
       <c r="G57" s="3">
-        <v>2227800</v>
+        <v>2250300</v>
       </c>
       <c r="H57" s="3">
-        <v>2720500</v>
+        <v>2747900</v>
       </c>
       <c r="I57" s="3">
-        <v>2838500</v>
+        <v>2867100</v>
       </c>
       <c r="J57" s="3">
-        <v>2674500</v>
+        <v>2701500</v>
       </c>
       <c r="K57" s="3">
         <v>2006500</v>
@@ -2708,25 +2708,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2141100</v>
+        <v>2162700</v>
       </c>
       <c r="E58" s="3">
-        <v>5946700</v>
+        <v>6006700</v>
       </c>
       <c r="F58" s="3">
-        <v>4726700</v>
+        <v>4774400</v>
       </c>
       <c r="G58" s="3">
-        <v>4480400</v>
+        <v>4525600</v>
       </c>
       <c r="H58" s="3">
-        <v>5105000</v>
+        <v>5156500</v>
       </c>
       <c r="I58" s="3">
-        <v>4535800</v>
+        <v>4581500</v>
       </c>
       <c r="J58" s="3">
-        <v>3373400</v>
+        <v>3407500</v>
       </c>
       <c r="K58" s="3">
         <v>1899000</v>
@@ -2753,25 +2753,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2860400</v>
+        <v>2889200</v>
       </c>
       <c r="E59" s="3">
-        <v>2353900</v>
+        <v>2377600</v>
       </c>
       <c r="F59" s="3">
-        <v>1728600</v>
+        <v>1746100</v>
       </c>
       <c r="G59" s="3">
-        <v>2027400</v>
+        <v>2047900</v>
       </c>
       <c r="H59" s="3">
-        <v>1574900</v>
+        <v>1590700</v>
       </c>
       <c r="I59" s="3">
-        <v>2060200</v>
+        <v>2081000</v>
       </c>
       <c r="J59" s="3">
-        <v>1150000</v>
+        <v>1161600</v>
       </c>
       <c r="K59" s="3">
         <v>1677900</v>
@@ -2798,25 +2798,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>8611800</v>
+        <v>8698600</v>
       </c>
       <c r="E60" s="3">
-        <v>12321100</v>
+        <v>12445400</v>
       </c>
       <c r="F60" s="3">
-        <v>9503800</v>
+        <v>9599600</v>
       </c>
       <c r="G60" s="3">
-        <v>8735600</v>
+        <v>8823800</v>
       </c>
       <c r="H60" s="3">
-        <v>9400300</v>
+        <v>9495100</v>
       </c>
       <c r="I60" s="3">
-        <v>9434500</v>
+        <v>9529700</v>
       </c>
       <c r="J60" s="3">
-        <v>7198000</v>
+        <v>7270600</v>
       </c>
       <c r="K60" s="3">
         <v>5583400</v>
@@ -2843,25 +2843,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>43917300</v>
+        <v>44360200</v>
       </c>
       <c r="E61" s="3">
-        <v>36540000</v>
+        <v>36908600</v>
       </c>
       <c r="F61" s="3">
-        <v>33727000</v>
+        <v>34067200</v>
       </c>
       <c r="G61" s="3">
-        <v>31636200</v>
+        <v>31955300</v>
       </c>
       <c r="H61" s="3">
-        <v>31259400</v>
+        <v>31574700</v>
       </c>
       <c r="I61" s="3">
-        <v>32077800</v>
+        <v>32401400</v>
       </c>
       <c r="J61" s="3">
-        <v>28335600</v>
+        <v>28621400</v>
       </c>
       <c r="K61" s="3">
         <v>30711100</v>
@@ -2888,25 +2888,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>10163300</v>
+        <v>10265800</v>
       </c>
       <c r="E62" s="3">
-        <v>9608700</v>
+        <v>9705600</v>
       </c>
       <c r="F62" s="3">
-        <v>8381500</v>
+        <v>8466000</v>
       </c>
       <c r="G62" s="3">
-        <v>8329000</v>
+        <v>8413000</v>
       </c>
       <c r="H62" s="3">
-        <v>8081200</v>
+        <v>8162700</v>
       </c>
       <c r="I62" s="3">
-        <v>7990100</v>
+        <v>8070700</v>
       </c>
       <c r="J62" s="3">
-        <v>7616300</v>
+        <v>7693100</v>
       </c>
       <c r="K62" s="3">
         <v>8829500</v>
@@ -3068,25 +3068,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>69582700</v>
+        <v>70284500</v>
       </c>
       <c r="E66" s="3">
-        <v>58561700</v>
+        <v>59152300</v>
       </c>
       <c r="F66" s="3">
-        <v>51703300</v>
+        <v>52224800</v>
       </c>
       <c r="G66" s="3">
-        <v>50213000</v>
+        <v>50719500</v>
       </c>
       <c r="H66" s="3">
-        <v>49931700</v>
+        <v>50435300</v>
       </c>
       <c r="I66" s="3">
-        <v>50708600</v>
+        <v>51220000</v>
       </c>
       <c r="J66" s="3">
-        <v>44499500</v>
+        <v>44948300</v>
       </c>
       <c r="K66" s="3">
         <v>46378900</v>
@@ -3222,25 +3222,25 @@
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>1821200</v>
+        <v>1839500</v>
       </c>
       <c r="E70" s="3">
-        <v>1821200</v>
+        <v>1839500</v>
       </c>
       <c r="F70" s="3">
-        <v>2541200</v>
+        <v>2566800</v>
       </c>
       <c r="G70" s="3">
-        <v>2900500</v>
+        <v>2929700</v>
       </c>
       <c r="H70" s="3">
-        <v>2900500</v>
+        <v>2929700</v>
       </c>
       <c r="I70" s="3">
-        <v>2900500</v>
+        <v>2929700</v>
       </c>
       <c r="J70" s="3">
-        <v>2900500</v>
+        <v>2929700</v>
       </c>
       <c r="K70" s="3">
         <v>2893500</v>
@@ -3312,25 +3312,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-2184100</v>
+        <v>-2206100</v>
       </c>
       <c r="E72" s="3">
-        <v>596900</v>
+        <v>602900</v>
       </c>
       <c r="F72" s="3">
-        <v>2749600</v>
+        <v>2777300</v>
       </c>
       <c r="G72" s="3">
-        <v>3911300</v>
+        <v>3950700</v>
       </c>
       <c r="H72" s="3">
-        <v>2882200</v>
+        <v>2911300</v>
       </c>
       <c r="I72" s="3">
-        <v>2020900</v>
+        <v>2041200</v>
       </c>
       <c r="J72" s="3">
-        <v>1182800</v>
+        <v>1194700</v>
       </c>
       <c r="K72" s="3">
         <v>827300</v>
@@ -3492,25 +3492,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>19715800</v>
+        <v>19914800</v>
       </c>
       <c r="E76" s="3">
-        <v>22949400</v>
+        <v>23180900</v>
       </c>
       <c r="F76" s="3">
-        <v>21705400</v>
+        <v>21924300</v>
       </c>
       <c r="G76" s="3">
-        <v>19981100</v>
+        <v>20182700</v>
       </c>
       <c r="H76" s="3">
-        <v>19518300</v>
+        <v>19715300</v>
       </c>
       <c r="I76" s="3">
-        <v>18479900</v>
+        <v>18666300</v>
       </c>
       <c r="J76" s="3">
-        <v>15346900</v>
+        <v>15501800</v>
       </c>
       <c r="K76" s="3">
         <v>14741600</v>
@@ -3632,25 +3632,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>2061700</v>
+        <v>2082500</v>
       </c>
       <c r="E81" s="3">
-        <v>467100</v>
+        <v>471800</v>
       </c>
       <c r="F81" s="3">
-        <v>1322700</v>
+        <v>1336000</v>
       </c>
       <c r="G81" s="3">
-        <v>3248100</v>
+        <v>3280800</v>
       </c>
       <c r="H81" s="3">
-        <v>2897500</v>
+        <v>2926800</v>
       </c>
       <c r="I81" s="3">
-        <v>2579100</v>
+        <v>2605100</v>
       </c>
       <c r="J81" s="3">
-        <v>2184100</v>
+        <v>2206100</v>
       </c>
       <c r="K81" s="3">
         <v>90100</v>
@@ -3696,25 +3696,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>2024500</v>
+        <v>2044900</v>
       </c>
       <c r="E83" s="3">
-        <v>1883100</v>
+        <v>1902100</v>
       </c>
       <c r="F83" s="3">
-        <v>1837900</v>
+        <v>1856500</v>
       </c>
       <c r="G83" s="3">
-        <v>1887500</v>
+        <v>1906500</v>
       </c>
       <c r="H83" s="3">
-        <v>1795700</v>
+        <v>1813800</v>
       </c>
       <c r="I83" s="3">
-        <v>1712600</v>
+        <v>1729900</v>
       </c>
       <c r="J83" s="3">
-        <v>1497600</v>
+        <v>1512700</v>
       </c>
       <c r="K83" s="3">
         <v>1409700</v>
@@ -3966,25 +3966,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>5296600</v>
+        <v>5350000</v>
       </c>
       <c r="E89" s="3">
-        <v>4645800</v>
+        <v>4692700</v>
       </c>
       <c r="F89" s="3">
-        <v>5021200</v>
+        <v>5071800</v>
       </c>
       <c r="G89" s="3">
-        <v>5143600</v>
+        <v>5195500</v>
       </c>
       <c r="H89" s="3">
-        <v>5161100</v>
+        <v>5213100</v>
       </c>
       <c r="I89" s="3">
-        <v>4777000</v>
+        <v>4825200</v>
       </c>
       <c r="J89" s="3">
-        <v>3811400</v>
+        <v>3849900</v>
       </c>
       <c r="K89" s="3">
         <v>3685200</v>
@@ -4030,25 +4030,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-5938700</v>
+        <v>-5998600</v>
       </c>
       <c r="E91" s="3">
-        <v>-4902400</v>
+        <v>-4951800</v>
       </c>
       <c r="F91" s="3">
-        <v>-4317200</v>
+        <v>-4360700</v>
       </c>
       <c r="G91" s="3">
-        <v>-5928500</v>
+        <v>-5988300</v>
       </c>
       <c r="H91" s="3">
-        <v>-5962700</v>
+        <v>-6022900</v>
       </c>
       <c r="I91" s="3">
-        <v>-7224900</v>
+        <v>-7297800</v>
       </c>
       <c r="J91" s="3">
-        <v>-5486800</v>
+        <v>-5542200</v>
       </c>
       <c r="K91" s="3">
         <v>-3854600</v>
@@ -4165,25 +4165,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-8954300</v>
+        <v>-9044600</v>
       </c>
       <c r="E94" s="3">
-        <v>-5107900</v>
+        <v>-5159400</v>
       </c>
       <c r="F94" s="3">
-        <v>-5620200</v>
+        <v>-5676900</v>
       </c>
       <c r="G94" s="3">
-        <v>-4410500</v>
+        <v>-4454900</v>
       </c>
       <c r="H94" s="3">
-        <v>-5008000</v>
+        <v>-5058500</v>
       </c>
       <c r="I94" s="3">
-        <v>-7301400</v>
+        <v>-7375100</v>
       </c>
       <c r="J94" s="3">
-        <v>-2695700</v>
+        <v>-2722900</v>
       </c>
       <c r="K94" s="3">
         <v>-13655400</v>
@@ -4229,25 +4229,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-2098100</v>
+        <v>-2119300</v>
       </c>
       <c r="E96" s="3">
-        <v>-2403500</v>
+        <v>-2427700</v>
       </c>
       <c r="F96" s="3">
-        <v>-2520100</v>
+        <v>-2545500</v>
       </c>
       <c r="G96" s="3">
-        <v>-2292700</v>
+        <v>-2315800</v>
       </c>
       <c r="H96" s="3">
-        <v>-1426900</v>
+        <v>-1441300</v>
       </c>
       <c r="I96" s="3">
-        <v>-1260000</v>
+        <v>-1272700</v>
       </c>
       <c r="J96" s="3">
-        <v>-1088800</v>
+        <v>-1099700</v>
       </c>
       <c r="K96" s="3">
         <v>-1116700</v>
@@ -4409,25 +4409,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>5897900</v>
+        <v>5957300</v>
       </c>
       <c r="E100" s="3">
-        <v>354900</v>
+        <v>358500</v>
       </c>
       <c r="F100" s="3">
-        <v>-64100</v>
+        <v>-64800</v>
       </c>
       <c r="G100" s="3">
-        <v>-583000</v>
+        <v>-588900</v>
       </c>
       <c r="H100" s="3">
-        <v>505000</v>
+        <v>510100</v>
       </c>
       <c r="I100" s="3">
-        <v>2002600</v>
+        <v>2022800</v>
       </c>
       <c r="J100" s="3">
-        <v>-1034100</v>
+        <v>-1044500</v>
       </c>
       <c r="K100" s="3">
         <v>10183200</v>
@@ -4454,25 +4454,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-11700</v>
+        <v>-11800</v>
       </c>
       <c r="E101" s="3">
-        <v>68500</v>
+        <v>69200</v>
       </c>
       <c r="F101" s="3">
-        <v>38600</v>
+        <v>39000</v>
       </c>
       <c r="G101" s="3">
-        <v>-13800</v>
+        <v>-14000</v>
       </c>
       <c r="H101" s="3">
         <v>-4400</v>
       </c>
       <c r="I101" s="3">
-        <v>53200</v>
+        <v>53700</v>
       </c>
       <c r="J101" s="3">
-        <v>-28400</v>
+        <v>-28700</v>
       </c>
       <c r="K101" s="3">
         <v>-92300</v>
@@ -4499,25 +4499,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>2228500</v>
+        <v>2251000</v>
       </c>
       <c r="E102" s="3">
-        <v>-38600</v>
+        <v>-39000</v>
       </c>
       <c r="F102" s="3">
-        <v>-624500</v>
+        <v>-630800</v>
       </c>
       <c r="G102" s="3">
-        <v>136300</v>
+        <v>137700</v>
       </c>
       <c r="H102" s="3">
-        <v>653700</v>
+        <v>660300</v>
       </c>
       <c r="I102" s="3">
-        <v>-468600</v>
+        <v>-473300</v>
       </c>
       <c r="J102" s="3">
-        <v>53200</v>
+        <v>53700</v>
       </c>
       <c r="K102" s="3">
         <v>120700</v>

--- a/AAII_Financials/Yearly/TRP_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/TRP_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="92">
   <si>
     <t>TRP</t>
   </si>
@@ -728,25 +728,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>11729200</v>
+        <v>12065500</v>
       </c>
       <c r="E8" s="3">
-        <v>11024700</v>
+        <v>11066000</v>
       </c>
       <c r="F8" s="3">
-        <v>9854300</v>
+        <v>10578500</v>
       </c>
       <c r="G8" s="3">
-        <v>9568700</v>
+        <v>10201700</v>
       </c>
       <c r="H8" s="3">
-        <v>9757100</v>
+        <v>10219500</v>
       </c>
       <c r="I8" s="3">
-        <v>10069200</v>
+        <v>10024600</v>
       </c>
       <c r="J8" s="3">
-        <v>9899900</v>
+        <v>10724200</v>
       </c>
       <c r="K8" s="3">
         <v>9121800</v>
@@ -773,25 +773,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>3597400</v>
+        <v>4005700</v>
       </c>
       <c r="E9" s="3">
-        <v>3630500</v>
+        <v>3964000</v>
       </c>
       <c r="F9" s="3">
-        <v>3016600</v>
+        <v>3243000</v>
       </c>
       <c r="G9" s="3">
-        <v>2854600</v>
+        <v>3043500</v>
       </c>
       <c r="H9" s="3">
-        <v>2877500</v>
+        <v>3216600</v>
       </c>
       <c r="I9" s="3">
-        <v>2643400</v>
+        <v>3660600</v>
       </c>
       <c r="J9" s="3">
-        <v>2875200</v>
+        <v>4939900</v>
       </c>
       <c r="K9" s="3">
         <v>2807000</v>
@@ -818,25 +818,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>8131800</v>
+        <v>8059800</v>
       </c>
       <c r="E10" s="3">
-        <v>7394200</v>
+        <v>7102000</v>
       </c>
       <c r="F10" s="3">
-        <v>6837700</v>
+        <v>7335500</v>
       </c>
       <c r="G10" s="3">
-        <v>6714100</v>
+        <v>7158200</v>
       </c>
       <c r="H10" s="3">
-        <v>6879700</v>
+        <v>7002900</v>
       </c>
       <c r="I10" s="3">
-        <v>7425900</v>
+        <v>6364000</v>
       </c>
       <c r="J10" s="3">
-        <v>7024700</v>
+        <v>5784300</v>
       </c>
       <c r="K10" s="3">
         <v>6314800</v>
@@ -972,25 +972,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>1569400</v>
+        <v>1553000</v>
       </c>
       <c r="E14" s="3">
-        <v>2577100</v>
+        <v>2631900</v>
       </c>
       <c r="F14" s="3">
-        <v>2042700</v>
+        <v>2782300</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>38500</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
+        <v>93300</v>
       </c>
       <c r="I14" s="3">
-        <v>589600</v>
+        <v>462400</v>
       </c>
       <c r="J14" s="3">
-        <v>925300</v>
+        <v>499200</v>
       </c>
       <c r="K14" s="3">
         <v>1088300</v>
@@ -1017,25 +1017,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>2044900</v>
+        <v>2103500</v>
       </c>
       <c r="E15" s="3">
-        <v>1902100</v>
+        <v>1909200</v>
       </c>
       <c r="F15" s="3">
-        <v>1856500</v>
+        <v>1992900</v>
       </c>
       <c r="G15" s="3">
-        <v>1906500</v>
+        <v>2032600</v>
       </c>
       <c r="H15" s="3">
-        <v>1813800</v>
+        <v>1899700</v>
       </c>
       <c r="I15" s="3">
-        <v>1729900</v>
+        <v>1722200</v>
       </c>
       <c r="J15" s="3">
-        <v>1512700</v>
+        <v>1638700</v>
       </c>
       <c r="K15" s="3">
         <v>1409700</v>
@@ -1078,25 +1078,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>8252500</v>
+        <v>6899000</v>
       </c>
       <c r="E17" s="3">
-        <v>9127000</v>
+        <v>6534600</v>
       </c>
       <c r="F17" s="3">
-        <v>7549500</v>
+        <v>5299900</v>
       </c>
       <c r="G17" s="3">
-        <v>5296300</v>
+        <v>5646700</v>
       </c>
       <c r="H17" s="3">
-        <v>5498000</v>
+        <v>5758500</v>
       </c>
       <c r="I17" s="3">
-        <v>6477000</v>
+        <v>5861300</v>
       </c>
       <c r="J17" s="3">
-        <v>7485500</v>
+        <v>7106400</v>
       </c>
       <c r="K17" s="3">
         <v>7287500</v>
@@ -1123,25 +1123,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>3476600</v>
+        <v>5166500</v>
       </c>
       <c r="E18" s="3">
-        <v>1897700</v>
+        <v>4531500</v>
       </c>
       <c r="F18" s="3">
-        <v>2304800</v>
+        <v>5278600</v>
       </c>
       <c r="G18" s="3">
-        <v>4272400</v>
+        <v>4555000</v>
       </c>
       <c r="H18" s="3">
-        <v>4259100</v>
+        <v>4460900</v>
       </c>
       <c r="I18" s="3">
-        <v>3592200</v>
+        <v>4163300</v>
       </c>
       <c r="J18" s="3">
-        <v>2414400</v>
+        <v>3617800</v>
       </c>
       <c r="K18" s="3">
         <v>1834200</v>
@@ -1187,25 +1187,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>1869700</v>
+        <v>-1720400</v>
       </c>
       <c r="E20" s="3">
-        <v>1018800</v>
+        <v>-914700</v>
       </c>
       <c r="F20" s="3">
-        <v>1026900</v>
+        <v>-928500</v>
       </c>
       <c r="G20" s="3">
-        <v>1127000</v>
+        <v>-1095600</v>
       </c>
       <c r="H20" s="3">
-        <v>1276400</v>
+        <v>-1305300</v>
       </c>
       <c r="I20" s="3">
-        <v>982000</v>
+        <v>-723300</v>
       </c>
       <c r="J20" s="3">
-        <v>1541400</v>
+        <v>-1040600</v>
       </c>
       <c r="K20" s="3">
         <v>143200</v>
@@ -1232,25 +1232,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>7392000</v>
+        <v>8990400</v>
       </c>
       <c r="E21" s="3">
-        <v>4819300</v>
+        <v>7355400</v>
       </c>
       <c r="F21" s="3">
-        <v>5188800</v>
+        <v>8200000</v>
       </c>
       <c r="G21" s="3">
-        <v>7306600</v>
+        <v>7683300</v>
       </c>
       <c r="H21" s="3">
-        <v>7350000</v>
+        <v>7665900</v>
       </c>
       <c r="I21" s="3">
-        <v>6304700</v>
+        <v>6608800</v>
       </c>
       <c r="J21" s="3">
-        <v>5469100</v>
+        <v>6297000</v>
       </c>
       <c r="K21" s="3">
         <v>3395100</v>
@@ -1277,25 +1277,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>2394600</v>
+        <v>2470800</v>
       </c>
       <c r="E22" s="3">
-        <v>1905100</v>
+        <v>1912200</v>
       </c>
       <c r="F22" s="3">
-        <v>1737200</v>
+        <v>1864900</v>
       </c>
       <c r="G22" s="3">
-        <v>1640100</v>
+        <v>1748500</v>
       </c>
       <c r="H22" s="3">
-        <v>1717300</v>
+        <v>1798700</v>
       </c>
       <c r="I22" s="3">
-        <v>1667300</v>
+        <v>1659900</v>
       </c>
       <c r="J22" s="3">
-        <v>1522300</v>
+        <v>1649800</v>
       </c>
       <c r="K22" s="3">
         <v>1369000</v>
@@ -1322,25 +1322,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>2951800</v>
+        <v>3036400</v>
       </c>
       <c r="E23" s="3">
-        <v>1011400</v>
+        <v>1015200</v>
       </c>
       <c r="F23" s="3">
-        <v>1594400</v>
+        <v>1711600</v>
       </c>
       <c r="G23" s="3">
-        <v>3759300</v>
+        <v>4008000</v>
       </c>
       <c r="H23" s="3">
-        <v>3818200</v>
+        <v>3999100</v>
       </c>
       <c r="I23" s="3">
-        <v>2906900</v>
+        <v>2894000</v>
       </c>
       <c r="J23" s="3">
-        <v>2433600</v>
+        <v>2636200</v>
       </c>
       <c r="K23" s="3">
         <v>608500</v>
@@ -1367,25 +1367,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>693400</v>
+        <v>713300</v>
       </c>
       <c r="E24" s="3">
-        <v>433600</v>
+        <v>435200</v>
       </c>
       <c r="F24" s="3">
-        <v>88300</v>
+        <v>94800</v>
       </c>
       <c r="G24" s="3">
-        <v>142800</v>
+        <v>152300</v>
       </c>
       <c r="H24" s="3">
-        <v>555000</v>
+        <v>581300</v>
       </c>
       <c r="I24" s="3">
-        <v>440900</v>
+        <v>316600</v>
       </c>
       <c r="J24" s="3">
-        <v>526300</v>
+        <v>-71000</v>
       </c>
       <c r="K24" s="3">
         <v>255900</v>
@@ -1457,25 +1457,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>2258400</v>
+        <v>2323100</v>
       </c>
       <c r="E26" s="3">
-        <v>577800</v>
+        <v>580000</v>
       </c>
       <c r="F26" s="3">
-        <v>1506100</v>
+        <v>1616800</v>
       </c>
       <c r="G26" s="3">
-        <v>3616500</v>
+        <v>3855800</v>
       </c>
       <c r="H26" s="3">
-        <v>3263200</v>
+        <v>3417800</v>
       </c>
       <c r="I26" s="3">
-        <v>2466000</v>
+        <v>2577400</v>
       </c>
       <c r="J26" s="3">
-        <v>1907300</v>
+        <v>2707200</v>
       </c>
       <c r="K26" s="3">
         <v>352600</v>
@@ -1502,25 +1502,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>2082500</v>
+        <v>2142200</v>
       </c>
       <c r="E27" s="3">
-        <v>471800</v>
+        <v>473600</v>
       </c>
       <c r="F27" s="3">
-        <v>1336000</v>
+        <v>1434200</v>
       </c>
       <c r="G27" s="3">
-        <v>3280800</v>
+        <v>3497900</v>
       </c>
       <c r="H27" s="3">
-        <v>2926800</v>
+        <v>3065400</v>
       </c>
       <c r="I27" s="3">
-        <v>2482200</v>
+        <v>2593600</v>
       </c>
       <c r="J27" s="3">
-        <v>1614300</v>
+        <v>2389800</v>
       </c>
       <c r="K27" s="3">
         <v>90100</v>
@@ -1591,14 +1591,14 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>8</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
       </c>
       <c r="G29" s="3">
         <v>0</v>
@@ -1607,10 +1607,10 @@
         <v>0</v>
       </c>
       <c r="I29" s="3">
-        <v>122900</v>
+        <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>591800</v>
+        <v>0</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
@@ -1727,25 +1727,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-1869700</v>
+        <v>1720400</v>
       </c>
       <c r="E32" s="3">
-        <v>-1018800</v>
+        <v>914700</v>
       </c>
       <c r="F32" s="3">
-        <v>-1026900</v>
+        <v>928500</v>
       </c>
       <c r="G32" s="3">
-        <v>-1127000</v>
+        <v>1095600</v>
       </c>
       <c r="H32" s="3">
-        <v>-1276400</v>
+        <v>1305300</v>
       </c>
       <c r="I32" s="3">
-        <v>-982000</v>
+        <v>723300</v>
       </c>
       <c r="J32" s="3">
-        <v>-1541400</v>
+        <v>1040600</v>
       </c>
       <c r="K32" s="3">
         <v>-143200</v>
@@ -1772,25 +1772,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>2082500</v>
+        <v>2212600</v>
       </c>
       <c r="E33" s="3">
-        <v>471800</v>
+        <v>552700</v>
       </c>
       <c r="F33" s="3">
-        <v>1336000</v>
+        <v>1544900</v>
       </c>
       <c r="G33" s="3">
-        <v>3280800</v>
+        <v>3622700</v>
       </c>
       <c r="H33" s="3">
-        <v>2926800</v>
+        <v>3191900</v>
       </c>
       <c r="I33" s="3">
-        <v>2605100</v>
+        <v>2713000</v>
       </c>
       <c r="J33" s="3">
-        <v>2206100</v>
+        <v>2517400</v>
       </c>
       <c r="K33" s="3">
         <v>90100</v>
@@ -1862,25 +1862,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>2082500</v>
+        <v>2212600</v>
       </c>
       <c r="E35" s="3">
-        <v>471800</v>
+        <v>552700</v>
       </c>
       <c r="F35" s="3">
-        <v>1336000</v>
+        <v>1544900</v>
       </c>
       <c r="G35" s="3">
-        <v>3280800</v>
+        <v>3622700</v>
       </c>
       <c r="H35" s="3">
-        <v>2926800</v>
+        <v>3191900</v>
       </c>
       <c r="I35" s="3">
-        <v>2605100</v>
+        <v>2713000</v>
       </c>
       <c r="J35" s="3">
-        <v>2206100</v>
+        <v>2517400</v>
       </c>
       <c r="K35" s="3">
         <v>90100</v>
@@ -1995,25 +1995,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>2707400</v>
+        <v>2785000</v>
       </c>
       <c r="E41" s="3">
-        <v>456400</v>
+        <v>458100</v>
       </c>
       <c r="F41" s="3">
-        <v>495400</v>
+        <v>531800</v>
       </c>
       <c r="G41" s="3">
-        <v>1126200</v>
+        <v>1200800</v>
       </c>
       <c r="H41" s="3">
-        <v>988600</v>
+        <v>1035400</v>
       </c>
       <c r="I41" s="3">
-        <v>328300</v>
+        <v>326900</v>
       </c>
       <c r="J41" s="3">
-        <v>801600</v>
+        <v>868400</v>
       </c>
       <c r="K41" s="3">
         <v>738600</v>
@@ -2039,26 +2039,26 @@
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>8</v>
+      <c r="D42" s="3">
+        <v>958600</v>
+      </c>
+      <c r="E42" s="3">
+        <v>449200</v>
+      </c>
+      <c r="F42" s="3">
+        <v>125600</v>
       </c>
       <c r="G42" s="3">
-        <v>138400</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>8</v>
+        <v>147500</v>
+      </c>
+      <c r="H42" s="3">
+        <v>138800</v>
       </c>
       <c r="I42" s="3">
-        <v>527800</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>8</v>
+        <v>527700</v>
+      </c>
+      <c r="J42" s="3">
+        <v>257600</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>8</v>
@@ -2085,25 +2085,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>3209400</v>
+        <v>3709600</v>
       </c>
       <c r="E43" s="3">
-        <v>2781800</v>
+        <v>3373700</v>
       </c>
       <c r="F43" s="3">
-        <v>3320600</v>
+        <v>4070400</v>
       </c>
       <c r="G43" s="3">
-        <v>1688600</v>
+        <v>1800300</v>
       </c>
       <c r="H43" s="3">
-        <v>1895500</v>
+        <v>1985300</v>
       </c>
       <c r="I43" s="3">
-        <v>1983100</v>
+        <v>1974300</v>
       </c>
       <c r="J43" s="3">
-        <v>1856500</v>
+        <v>2011000</v>
       </c>
       <c r="K43" s="3">
         <v>1508500</v>
@@ -2130,25 +2130,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>722900</v>
+        <v>743600</v>
       </c>
       <c r="E44" s="3">
-        <v>689000</v>
+        <v>691600</v>
       </c>
       <c r="F44" s="3">
-        <v>532900</v>
+        <v>572100</v>
       </c>
       <c r="G44" s="3">
-        <v>463000</v>
+        <v>493600</v>
       </c>
       <c r="H44" s="3">
-        <v>332700</v>
+        <v>348500</v>
       </c>
       <c r="I44" s="3">
-        <v>317300</v>
+        <v>315900</v>
       </c>
       <c r="J44" s="3">
-        <v>278200</v>
+        <v>301400</v>
       </c>
       <c r="K44" s="3">
         <v>267500</v>
@@ -2175,25 +2175,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1731300</v>
+        <v>253700</v>
       </c>
       <c r="E45" s="3">
-        <v>1470000</v>
+        <v>279300</v>
       </c>
       <c r="F45" s="3">
-        <v>1115200</v>
+        <v>261600</v>
       </c>
       <c r="G45" s="3">
-        <v>412200</v>
+        <v>229200</v>
       </c>
       <c r="H45" s="3">
-        <v>2415200</v>
+        <v>2304500</v>
       </c>
       <c r="I45" s="3">
-        <v>623500</v>
+        <v>548200</v>
       </c>
       <c r="J45" s="3">
-        <v>508700</v>
+        <v>127600</v>
       </c>
       <c r="K45" s="3">
         <v>3362400</v>
@@ -2220,25 +2220,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>8371000</v>
+        <v>8611000</v>
       </c>
       <c r="E46" s="3">
-        <v>5397200</v>
+        <v>5417400</v>
       </c>
       <c r="F46" s="3">
-        <v>5464100</v>
+        <v>5865700</v>
       </c>
       <c r="G46" s="3">
-        <v>3828500</v>
+        <v>4081800</v>
       </c>
       <c r="H46" s="3">
-        <v>5632000</v>
+        <v>5898800</v>
       </c>
       <c r="I46" s="3">
-        <v>3779900</v>
+        <v>3763200</v>
       </c>
       <c r="J46" s="3">
-        <v>3445000</v>
+        <v>3731800</v>
       </c>
       <c r="K46" s="3">
         <v>5877100</v>
@@ -2265,25 +2265,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>9594500</v>
+        <v>7897700</v>
       </c>
       <c r="E47" s="3">
-        <v>8675100</v>
+        <v>7102000</v>
       </c>
       <c r="F47" s="3">
-        <v>6572000</v>
+        <v>6682800</v>
       </c>
       <c r="G47" s="3">
-        <v>6055200</v>
+        <v>5255100</v>
       </c>
       <c r="H47" s="3">
-        <v>5844700</v>
+        <v>5017600</v>
       </c>
       <c r="I47" s="3">
-        <v>6240700</v>
+        <v>5256000</v>
       </c>
       <c r="J47" s="3">
-        <v>5413400</v>
+        <v>5134400</v>
       </c>
       <c r="K47" s="3">
         <v>4843300</v>
@@ -2310,25 +2310,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>59307600</v>
+        <v>61008000</v>
       </c>
       <c r="E48" s="3">
-        <v>55900200</v>
+        <v>56109700</v>
       </c>
       <c r="F48" s="3">
-        <v>51661700</v>
+        <v>55458400</v>
       </c>
       <c r="G48" s="3">
-        <v>51362100</v>
+        <v>54759800</v>
       </c>
       <c r="H48" s="3">
-        <v>48207100</v>
+        <v>50491300</v>
       </c>
       <c r="I48" s="3">
-        <v>48953500</v>
+        <v>48736600</v>
       </c>
       <c r="J48" s="3">
-        <v>42162200</v>
+        <v>45672500</v>
       </c>
       <c r="K48" s="3">
         <v>39603900</v>
@@ -2355,25 +2355,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>9224900</v>
+        <v>9489400</v>
       </c>
       <c r="E49" s="3">
-        <v>9453900</v>
+        <v>9489300</v>
       </c>
       <c r="F49" s="3">
-        <v>9261700</v>
+        <v>9942400</v>
       </c>
       <c r="G49" s="3">
-        <v>9333100</v>
+        <v>9950600</v>
       </c>
       <c r="H49" s="3">
-        <v>9486200</v>
+        <v>9935700</v>
       </c>
       <c r="I49" s="3">
-        <v>10436600</v>
+        <v>10390300</v>
       </c>
       <c r="J49" s="3">
-        <v>9631300</v>
+        <v>10433100</v>
       </c>
       <c r="K49" s="3">
         <v>10147600</v>
@@ -2490,25 +2490,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>5540700</v>
+        <v>4603100</v>
       </c>
       <c r="E52" s="3">
-        <v>4746400</v>
+        <v>3916700</v>
       </c>
       <c r="F52" s="3">
-        <v>3756400</v>
+        <v>3617600</v>
       </c>
       <c r="G52" s="3">
-        <v>3252900</v>
+        <v>3329100</v>
       </c>
       <c r="H52" s="3">
-        <v>3910200</v>
+        <v>2664500</v>
       </c>
       <c r="I52" s="3">
-        <v>3405200</v>
+        <v>2377400</v>
       </c>
       <c r="J52" s="3">
-        <v>2728000</v>
+        <v>2224700</v>
       </c>
       <c r="K52" s="3">
         <v>3542000</v>
@@ -2580,25 +2580,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>92038800</v>
+        <v>94677500</v>
       </c>
       <c r="E54" s="3">
-        <v>84172700</v>
+        <v>84488200</v>
       </c>
       <c r="F54" s="3">
-        <v>76715900</v>
+        <v>82353900</v>
       </c>
       <c r="G54" s="3">
-        <v>73831800</v>
+        <v>78716100</v>
       </c>
       <c r="H54" s="3">
-        <v>73080300</v>
+        <v>76543000</v>
       </c>
       <c r="I54" s="3">
-        <v>72816000</v>
+        <v>72493300</v>
       </c>
       <c r="J54" s="3">
-        <v>63379800</v>
+        <v>68656700</v>
       </c>
       <c r="K54" s="3">
         <v>64014000</v>
@@ -2663,25 +2663,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>3646700</v>
+        <v>4007200</v>
       </c>
       <c r="E57" s="3">
-        <v>4061100</v>
+        <v>3446800</v>
       </c>
       <c r="F57" s="3">
-        <v>3079100</v>
+        <v>3527500</v>
       </c>
       <c r="G57" s="3">
-        <v>2250300</v>
+        <v>2673000</v>
       </c>
       <c r="H57" s="3">
-        <v>2747900</v>
+        <v>2555100</v>
       </c>
       <c r="I57" s="3">
-        <v>2867100</v>
+        <v>2362700</v>
       </c>
       <c r="J57" s="3">
-        <v>2701500</v>
+        <v>2270200</v>
       </c>
       <c r="K57" s="3">
         <v>2006500</v>
@@ -2708,25 +2708,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2162700</v>
+        <v>2282200</v>
       </c>
       <c r="E58" s="3">
-        <v>6006700</v>
+        <v>6088300</v>
       </c>
       <c r="F58" s="3">
-        <v>4774400</v>
+        <v>5171900</v>
       </c>
       <c r="G58" s="3">
-        <v>4525600</v>
+        <v>4885400</v>
       </c>
       <c r="H58" s="3">
-        <v>5156500</v>
+        <v>5446300</v>
       </c>
       <c r="I58" s="3">
-        <v>4581500</v>
+        <v>4563400</v>
       </c>
       <c r="J58" s="3">
-        <v>3407500</v>
+        <v>3694300</v>
       </c>
       <c r="K58" s="3">
         <v>1899000</v>
@@ -2753,25 +2753,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2889200</v>
+        <v>1952900</v>
       </c>
       <c r="E59" s="3">
-        <v>2377600</v>
+        <v>2436100</v>
       </c>
       <c r="F59" s="3">
-        <v>1746100</v>
+        <v>1090500</v>
       </c>
       <c r="G59" s="3">
-        <v>2047900</v>
+        <v>1382000</v>
       </c>
       <c r="H59" s="3">
-        <v>1590700</v>
+        <v>1471000</v>
       </c>
       <c r="I59" s="3">
-        <v>2081000</v>
+        <v>2087900</v>
       </c>
       <c r="J59" s="3">
-        <v>1161600</v>
+        <v>1428900</v>
       </c>
       <c r="K59" s="3">
         <v>1677900</v>
@@ -2798,25 +2798,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>8698600</v>
+        <v>8948000</v>
       </c>
       <c r="E60" s="3">
-        <v>12445400</v>
+        <v>12492100</v>
       </c>
       <c r="F60" s="3">
-        <v>9599600</v>
+        <v>10305100</v>
       </c>
       <c r="G60" s="3">
-        <v>8823800</v>
+        <v>9407500</v>
       </c>
       <c r="H60" s="3">
-        <v>9495100</v>
+        <v>9945000</v>
       </c>
       <c r="I60" s="3">
-        <v>9529700</v>
+        <v>9487400</v>
       </c>
       <c r="J60" s="3">
-        <v>7270600</v>
+        <v>7875900</v>
       </c>
       <c r="K60" s="3">
         <v>5583400</v>
@@ -2843,25 +2843,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>44360200</v>
+        <v>45957600</v>
       </c>
       <c r="E61" s="3">
-        <v>36908600</v>
+        <v>37363900</v>
       </c>
       <c r="F61" s="3">
-        <v>34067200</v>
+        <v>36877400</v>
       </c>
       <c r="G61" s="3">
-        <v>31955300</v>
+        <v>34442800</v>
       </c>
       <c r="H61" s="3">
-        <v>31574700</v>
+        <v>33486400</v>
       </c>
       <c r="I61" s="3">
-        <v>32401400</v>
+        <v>32266600</v>
       </c>
       <c r="J61" s="3">
-        <v>28621400</v>
+        <v>31005200</v>
       </c>
       <c r="K61" s="3">
         <v>30711100</v>
@@ -2888,25 +2888,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>10265800</v>
+        <v>3999600</v>
       </c>
       <c r="E62" s="3">
-        <v>9705600</v>
+        <v>3668500</v>
       </c>
       <c r="F62" s="3">
-        <v>8466000</v>
+        <v>3645200</v>
       </c>
       <c r="G62" s="3">
-        <v>8413000</v>
+        <v>3485300</v>
       </c>
       <c r="H62" s="3">
-        <v>8162700</v>
+        <v>3146400</v>
       </c>
       <c r="I62" s="3">
-        <v>8070700</v>
+        <v>3104300</v>
       </c>
       <c r="J62" s="3">
-        <v>7693100</v>
+        <v>3714300</v>
       </c>
       <c r="K62" s="3">
         <v>8829500</v>
@@ -3068,25 +3068,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>70284500</v>
+        <v>65140100</v>
       </c>
       <c r="E66" s="3">
-        <v>59152300</v>
+        <v>59280900</v>
       </c>
       <c r="F66" s="3">
-        <v>52224800</v>
+        <v>55964100</v>
       </c>
       <c r="G66" s="3">
-        <v>50719500</v>
+        <v>52446200</v>
       </c>
       <c r="H66" s="3">
-        <v>50435300</v>
+        <v>51565300</v>
       </c>
       <c r="I66" s="3">
-        <v>51220000</v>
+        <v>49780100</v>
       </c>
       <c r="J66" s="3">
-        <v>44948300</v>
+        <v>47213900</v>
       </c>
       <c r="K66" s="3">
         <v>46378900</v>
@@ -3222,25 +3222,25 @@
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>1839500</v>
+        <v>1892300</v>
       </c>
       <c r="E70" s="3">
-        <v>1839500</v>
+        <v>1846400</v>
       </c>
       <c r="F70" s="3">
-        <v>2566800</v>
+        <v>2755500</v>
       </c>
       <c r="G70" s="3">
-        <v>2929700</v>
+        <v>3123500</v>
       </c>
       <c r="H70" s="3">
-        <v>2929700</v>
+        <v>3068500</v>
       </c>
       <c r="I70" s="3">
-        <v>2929700</v>
+        <v>2916700</v>
       </c>
       <c r="J70" s="3">
-        <v>2929700</v>
+        <v>3173600</v>
       </c>
       <c r="K70" s="3">
         <v>2893500</v>
@@ -3312,25 +3312,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-2206100</v>
+        <v>-2269400</v>
       </c>
       <c r="E72" s="3">
-        <v>602900</v>
+        <v>605100</v>
       </c>
       <c r="F72" s="3">
-        <v>2777300</v>
+        <v>2981500</v>
       </c>
       <c r="G72" s="3">
-        <v>3950700</v>
+        <v>4212100</v>
       </c>
       <c r="H72" s="3">
-        <v>2911300</v>
+        <v>3049300</v>
       </c>
       <c r="I72" s="3">
-        <v>2041200</v>
+        <v>2032200</v>
       </c>
       <c r="J72" s="3">
-        <v>1194700</v>
+        <v>1294200</v>
       </c>
       <c r="K72" s="3">
         <v>827300</v>
@@ -3492,25 +3492,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>19914800</v>
+        <v>20485700</v>
       </c>
       <c r="E76" s="3">
-        <v>23180900</v>
+        <v>23267700</v>
       </c>
       <c r="F76" s="3">
-        <v>21924300</v>
+        <v>23535500</v>
       </c>
       <c r="G76" s="3">
-        <v>20182700</v>
+        <v>21517800</v>
       </c>
       <c r="H76" s="3">
-        <v>19715300</v>
+        <v>20649400</v>
       </c>
       <c r="I76" s="3">
-        <v>18666300</v>
+        <v>18583600</v>
       </c>
       <c r="J76" s="3">
-        <v>15501800</v>
+        <v>16792400</v>
       </c>
       <c r="K76" s="3">
         <v>14741600</v>
@@ -3632,25 +3632,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>2082500</v>
+        <v>2212600</v>
       </c>
       <c r="E81" s="3">
-        <v>471800</v>
+        <v>552700</v>
       </c>
       <c r="F81" s="3">
-        <v>1336000</v>
+        <v>1544900</v>
       </c>
       <c r="G81" s="3">
-        <v>3280800</v>
+        <v>3622700</v>
       </c>
       <c r="H81" s="3">
-        <v>2926800</v>
+        <v>3191900</v>
       </c>
       <c r="I81" s="3">
-        <v>2605100</v>
+        <v>2713000</v>
       </c>
       <c r="J81" s="3">
-        <v>2206100</v>
+        <v>2517400</v>
       </c>
       <c r="K81" s="3">
         <v>90100</v>
@@ -3696,25 +3696,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>2044900</v>
+        <v>2103500</v>
       </c>
       <c r="E83" s="3">
-        <v>1902100</v>
+        <v>1909200</v>
       </c>
       <c r="F83" s="3">
-        <v>1856500</v>
+        <v>1992900</v>
       </c>
       <c r="G83" s="3">
-        <v>1906500</v>
+        <v>2032600</v>
       </c>
       <c r="H83" s="3">
-        <v>1813800</v>
+        <v>1899700</v>
       </c>
       <c r="I83" s="3">
-        <v>1729900</v>
+        <v>1722200</v>
       </c>
       <c r="J83" s="3">
-        <v>1512700</v>
+        <v>1638700</v>
       </c>
       <c r="K83" s="3">
         <v>1409700</v>
@@ -3966,25 +3966,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>5350000</v>
+        <v>5503400</v>
       </c>
       <c r="E89" s="3">
-        <v>4692700</v>
+        <v>4710300</v>
       </c>
       <c r="F89" s="3">
-        <v>5071800</v>
+        <v>5444500</v>
       </c>
       <c r="G89" s="3">
-        <v>5195500</v>
+        <v>5539200</v>
       </c>
       <c r="H89" s="3">
-        <v>5213100</v>
+        <v>5460100</v>
       </c>
       <c r="I89" s="3">
-        <v>4825200</v>
+        <v>4803800</v>
       </c>
       <c r="J89" s="3">
-        <v>3849900</v>
+        <v>4170400</v>
       </c>
       <c r="K89" s="3">
         <v>3685200</v>
@@ -4030,25 +4030,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-5998600</v>
+        <v>-6170500</v>
       </c>
       <c r="E91" s="3">
-        <v>-4951800</v>
+        <v>-4970400</v>
       </c>
       <c r="F91" s="3">
-        <v>-4360700</v>
+        <v>-4681200</v>
       </c>
       <c r="G91" s="3">
-        <v>-5988300</v>
+        <v>-6384400</v>
       </c>
       <c r="H91" s="3">
-        <v>-6022900</v>
+        <v>-6308200</v>
       </c>
       <c r="I91" s="3">
-        <v>-7297800</v>
+        <v>-7265500</v>
       </c>
       <c r="J91" s="3">
-        <v>-5542200</v>
+        <v>-6003600</v>
       </c>
       <c r="K91" s="3">
         <v>-3854600</v>
@@ -4165,25 +4165,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-9044600</v>
+        <v>-9303900</v>
       </c>
       <c r="E94" s="3">
-        <v>-5159400</v>
+        <v>-5178700</v>
       </c>
       <c r="F94" s="3">
-        <v>-5676900</v>
+        <v>-6094100</v>
       </c>
       <c r="G94" s="3">
-        <v>-4454900</v>
+        <v>-4749600</v>
       </c>
       <c r="H94" s="3">
-        <v>-5058500</v>
+        <v>-5298200</v>
       </c>
       <c r="I94" s="3">
-        <v>-7375100</v>
+        <v>-7342400</v>
       </c>
       <c r="J94" s="3">
-        <v>-2722900</v>
+        <v>-2949600</v>
       </c>
       <c r="K94" s="3">
         <v>-13655400</v>
@@ -4229,25 +4229,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-2119300</v>
+        <v>2110400</v>
       </c>
       <c r="E96" s="3">
-        <v>-2427700</v>
+        <v>2358500</v>
       </c>
       <c r="F96" s="3">
-        <v>-2545500</v>
+        <v>2621100</v>
       </c>
       <c r="G96" s="3">
-        <v>-2315800</v>
+        <v>2344200</v>
       </c>
       <c r="H96" s="3">
-        <v>-1441300</v>
+        <v>1386200</v>
       </c>
       <c r="I96" s="3">
-        <v>-1272700</v>
+        <v>1151300</v>
       </c>
       <c r="J96" s="3">
-        <v>-1099700</v>
+        <v>1067700</v>
       </c>
       <c r="K96" s="3">
         <v>-1116700</v>
@@ -4409,25 +4409,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>5957300</v>
+        <v>6128100</v>
       </c>
       <c r="E100" s="3">
-        <v>358500</v>
+        <v>359800</v>
       </c>
       <c r="F100" s="3">
-        <v>-64800</v>
+        <v>-69500</v>
       </c>
       <c r="G100" s="3">
-        <v>-588900</v>
+        <v>-627800</v>
       </c>
       <c r="H100" s="3">
-        <v>510100</v>
+        <v>534300</v>
       </c>
       <c r="I100" s="3">
-        <v>2022800</v>
+        <v>2013900</v>
       </c>
       <c r="J100" s="3">
-        <v>-1044500</v>
+        <v>-1131500</v>
       </c>
       <c r="K100" s="3">
         <v>10183200</v>
@@ -4454,25 +4454,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-11800</v>
+        <v>-12100</v>
       </c>
       <c r="E101" s="3">
-        <v>69200</v>
+        <v>69500</v>
       </c>
       <c r="F101" s="3">
-        <v>39000</v>
+        <v>41900</v>
       </c>
       <c r="G101" s="3">
-        <v>-14000</v>
+        <v>-14900</v>
       </c>
       <c r="H101" s="3">
-        <v>-4400</v>
+        <v>-4600</v>
       </c>
       <c r="I101" s="3">
-        <v>53700</v>
+        <v>53500</v>
       </c>
       <c r="J101" s="3">
-        <v>-28700</v>
+        <v>-31100</v>
       </c>
       <c r="K101" s="3">
         <v>-92300</v>
@@ -4499,25 +4499,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>2251000</v>
+        <v>2315600</v>
       </c>
       <c r="E102" s="3">
-        <v>-39000</v>
+        <v>-39200</v>
       </c>
       <c r="F102" s="3">
-        <v>-630800</v>
+        <v>-677200</v>
       </c>
       <c r="G102" s="3">
-        <v>137700</v>
+        <v>146800</v>
       </c>
       <c r="H102" s="3">
-        <v>660300</v>
+        <v>691600</v>
       </c>
       <c r="I102" s="3">
-        <v>-473300</v>
+        <v>-471200</v>
       </c>
       <c r="J102" s="3">
-        <v>53700</v>
+        <v>58200</v>
       </c>
       <c r="K102" s="3">
         <v>120700</v>

--- a/AAII_Financials/Yearly/TRP_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/TRP_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="92">
   <si>
     <t>TRP</t>
   </si>
@@ -656,209 +656,221 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41274</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40908</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>12065500</v>
+        <v>9570900</v>
       </c>
       <c r="E8" s="3">
-        <v>11066000</v>
+        <v>10046000</v>
       </c>
       <c r="F8" s="3">
+        <v>9094700</v>
+      </c>
+      <c r="G8" s="3">
         <v>10578500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>10201700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>10219500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>10024600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>10724200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>9121800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>8524500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>7995700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>6772100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>6027600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>6022200</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>4005700</v>
+        <v>3124000</v>
       </c>
       <c r="E9" s="3">
-        <v>3964000</v>
+        <v>3019000</v>
       </c>
       <c r="F9" s="3">
+        <v>3140200</v>
+      </c>
+      <c r="G9" s="3">
         <v>3243000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>3043500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>3216600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3660600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>4939900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2807000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2480100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2334000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2058500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1939900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2572800</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>8059800</v>
+        <v>6446900</v>
       </c>
       <c r="E10" s="3">
-        <v>7102000</v>
+        <v>7026900</v>
       </c>
       <c r="F10" s="3">
+        <v>5954500</v>
+      </c>
+      <c r="G10" s="3">
         <v>7335500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>7158200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>7002900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>6364000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>5784300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>6314800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>6044400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>5661800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4713600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4087600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>3449400</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -876,8 +888,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -920,9 +933,12 @@
       <c r="P12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -965,44 +981,47 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>1553000</v>
+        <v>-421900</v>
       </c>
       <c r="E14" s="3">
-        <v>2631900</v>
+        <v>1629500</v>
       </c>
       <c r="F14" s="3">
+        <v>2679100</v>
+      </c>
+      <c r="G14" s="3">
         <v>2782300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>38500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>93300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>462400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>499200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1088300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2827700</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>8</v>
@@ -1010,54 +1029,60 @@
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>2103500</v>
+        <v>1761800</v>
       </c>
       <c r="E15" s="3">
-        <v>1909200</v>
+        <v>1852100</v>
       </c>
       <c r="F15" s="3">
+        <v>1671300</v>
+      </c>
+      <c r="G15" s="3">
         <v>1992900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>2032600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1899700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1722200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1638700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1409700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1325300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1264700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1143200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1035100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>1020200</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1072,98 +1097,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>6899000</v>
+        <v>5532900</v>
       </c>
       <c r="E17" s="3">
-        <v>6534600</v>
+        <v>5539000</v>
       </c>
       <c r="F17" s="3">
+        <v>5348700</v>
+      </c>
+      <c r="G17" s="3">
         <v>5299900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>5646700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>5758500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5861300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>7106400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>7287500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>8701000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5411300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4558100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4091400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3908000</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>5166500</v>
+        <v>4038000</v>
       </c>
       <c r="E18" s="3">
-        <v>4531500</v>
+        <v>4506900</v>
       </c>
       <c r="F18" s="3">
+        <v>3746100</v>
+      </c>
+      <c r="G18" s="3">
         <v>5278600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>4555000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>4460900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>4163300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>3617800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1834200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-176500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2584400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2214000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1936200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2114200</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1181,233 +1213,249 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-1720400</v>
+        <v>-1525500</v>
       </c>
       <c r="E20" s="3">
-        <v>-914700</v>
+        <v>-1669700</v>
       </c>
       <c r="F20" s="3">
+        <v>-874100</v>
+      </c>
+      <c r="G20" s="3">
         <v>-928500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1095600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1305300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-723300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1040600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>143200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>461800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>573100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>501900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-310900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>399500</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>8990400</v>
+        <v>7325300</v>
       </c>
       <c r="E21" s="3">
-        <v>7355400</v>
+        <v>8028700</v>
       </c>
       <c r="F21" s="3">
+        <v>6291500</v>
+      </c>
+      <c r="G21" s="3">
         <v>8200000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>7683300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>7665900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>6608800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>6297000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3395100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1590200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>4417500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>3857100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2660800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>3538700</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>2470800</v>
+        <v>2098200</v>
       </c>
       <c r="E22" s="3">
-        <v>1912200</v>
+        <v>2245900</v>
       </c>
       <c r="F22" s="3">
+        <v>1699400</v>
+      </c>
+      <c r="G22" s="3">
         <v>1864900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1748500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1798700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1659900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1649800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1369000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1115800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>940500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>774400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>166400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>758200</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>3036400</v>
+        <v>4104700</v>
       </c>
       <c r="E23" s="3">
-        <v>1015200</v>
+        <v>2497300</v>
       </c>
       <c r="F23" s="3">
+        <v>350200</v>
+      </c>
+      <c r="G23" s="3">
         <v>1711600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>4008000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>3999100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2894000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2636200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>608500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-830500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2217000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1941500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1458900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1755400</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>713300</v>
+        <v>640800</v>
       </c>
       <c r="E24" s="3">
-        <v>435200</v>
+        <v>637600</v>
       </c>
       <c r="F24" s="3">
+        <v>237900</v>
+      </c>
+      <c r="G24" s="3">
         <v>94800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>152300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>581300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>316600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-71000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>255900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>25500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>652400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>470400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>350800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>441700</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1450,99 +1498,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>2323100</v>
+        <v>3463900</v>
       </c>
       <c r="E26" s="3">
-        <v>580000</v>
+        <v>1859700</v>
       </c>
       <c r="F26" s="3">
+        <v>112300</v>
+      </c>
+      <c r="G26" s="3">
         <v>1616800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>3855800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3417800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2577400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2707200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>352600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-856000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1564600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1471100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1108100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1313700</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3192800</v>
+      </c>
+      <c r="E27" s="3">
         <v>2142200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>473600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1434200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>3497900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>3065400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2593600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2389800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>90100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-931100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1368300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1317900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>977900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1172300</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1585,20 +1642,23 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>0</v>
+        <v>274500</v>
       </c>
       <c r="E29" s="3">
-        <v>0</v>
+        <v>463400</v>
       </c>
       <c r="F29" s="3">
-        <v>0</v>
+        <v>467700</v>
       </c>
       <c r="G29" s="3">
         <v>0</v>
@@ -1618,8 +1678,8 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-      <c r="M29" s="3" t="s">
-        <v>8</v>
+      <c r="M29" s="3">
+        <v>0</v>
       </c>
       <c r="N29" s="3" t="s">
         <v>8</v>
@@ -1630,9 +1690,12 @@
       <c r="P29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1675,9 +1738,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1720,99 +1786,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>1720400</v>
+        <v>1525500</v>
       </c>
       <c r="E32" s="3">
-        <v>914700</v>
+        <v>1669700</v>
       </c>
       <c r="F32" s="3">
+        <v>874100</v>
+      </c>
+      <c r="G32" s="3">
         <v>928500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1095600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1305300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>723300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1040600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-143200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-461800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-573100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-501900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>310900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-399500</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3265100</v>
+      </c>
+      <c r="E33" s="3">
         <v>2212600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>552700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1544900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>3622700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3191900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2713000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2517400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>90100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-931100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1368300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1317900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>977900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1172300</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1855,104 +1930,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3265100</v>
+      </c>
+      <c r="E35" s="3">
         <v>2212600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>552700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1544900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>3622700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3191900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2713000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2517400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>90100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-931100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1368300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1317900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>977900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1172300</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41274</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40908</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1970,8 +2054,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1989,79 +2074,83 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>556700</v>
+      </c>
+      <c r="E41" s="3">
         <v>2785000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>458100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>531800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1200800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1035400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>326900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>868400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>738600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>638200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>383900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>713600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>414800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>502400</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>958600</v>
+        <v>228700</v>
       </c>
       <c r="E42" s="3">
+        <v>431600</v>
+      </c>
+      <c r="F42" s="3">
         <v>449200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>125600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>147500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>138800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>527700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>257600</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L42" s="3" t="s">
         <v>8</v>
@@ -2075,327 +2164,351 @@
       <c r="O42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="P42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>3709600</v>
+        <v>2160800</v>
       </c>
       <c r="E43" s="3">
+        <v>2183800</v>
+      </c>
+      <c r="F43" s="3">
         <v>3373700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4070400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1800300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1985300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1974300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2011000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1508500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1041400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1030800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>863700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>791900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>840400</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>743600</v>
+        <v>519200</v>
       </c>
       <c r="E44" s="3">
+        <v>583800</v>
+      </c>
+      <c r="F44" s="3">
         <v>691600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>572100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>493600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>348500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>315900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>301400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>267500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>242500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>229200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>193200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>168600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>190500</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>253700</v>
+        <v>370400</v>
       </c>
       <c r="E45" s="3">
+        <v>2539700</v>
+      </c>
+      <c r="F45" s="3">
         <v>279300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>261600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>229200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2304500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>548200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>127600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3362400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1537800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1935100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>652000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>750500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>855800</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3984500</v>
+      </c>
+      <c r="E46" s="3">
         <v>8611000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5417400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5865700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4081800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5898800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3763200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3731800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5877100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2941900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2443900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2422600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2125900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2389200</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>7897700</v>
+        <v>7470600</v>
       </c>
       <c r="E47" s="3">
+        <v>7084500</v>
+      </c>
+      <c r="F47" s="3">
         <v>7102000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>6682800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>5255100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>5017600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>5256000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>5134400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>4843300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>4879800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>4583100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>4660500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>4327800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>4236000</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>61008000</v>
+        <v>53863500</v>
       </c>
       <c r="E48" s="3">
+        <v>52589300</v>
+      </c>
+      <c r="F48" s="3">
         <v>56109700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>55458400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>54759800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>50491300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>48736600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>45672500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>39603900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>67302600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>65589400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>28949900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>25378800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>93656500</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>9500700</v>
+      </c>
+      <c r="E49" s="3">
         <v>9489400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>9489300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>9942400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>9950600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>9935700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>10390300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>10433100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>10147600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5981400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4603500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3534200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2886200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4594800</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2438,9 +2551,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2483,54 +2599,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>4603100</v>
+        <v>4918500</v>
       </c>
       <c r="E52" s="3">
+        <v>13844900</v>
+      </c>
+      <c r="F52" s="3">
         <v>3916700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3617600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3329100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2664500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2377400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2224700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3542000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3169400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1733400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1924500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1665900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1738500</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2573,54 +2695,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>82179400</v>
+      </c>
+      <c r="E54" s="3">
         <v>94677500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>84488200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>82353900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>78716100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>76543000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>72493300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>68656700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>64014000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>48353900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>45945100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>41491800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>36384600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>36366500</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2638,8 +2766,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2657,278 +2786,297 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>4007200</v>
+        <v>2570800</v>
       </c>
       <c r="E57" s="3">
+        <v>2341300</v>
+      </c>
+      <c r="F57" s="3">
         <v>3446800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3527500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2673000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2555100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2362700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2270200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2006500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2745900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1274900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>666700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>694800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>534700</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2282200</v>
+        <v>2379000</v>
       </c>
       <c r="E58" s="3">
+        <v>2281500</v>
+      </c>
+      <c r="F58" s="3">
         <v>6088300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>5171900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>4885400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>5446300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>4563400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3694300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1899000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2827000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>3347500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2167000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2385600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2174900</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1952900</v>
+        <v>1779900</v>
       </c>
       <c r="E59" s="3">
+        <v>3633900</v>
+      </c>
+      <c r="F59" s="3">
         <v>2436100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1090500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1382000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1471000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2087900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1428900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1677900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1528000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1331400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1291000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1346700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1558000</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7305200</v>
+      </c>
+      <c r="E60" s="3">
         <v>8948000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>12492100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>10305100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>9407500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>9945000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>9487400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>7875900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5583400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5527800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>5950700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4124700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4427200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>4242200</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>45957600</v>
+        <v>39332400</v>
       </c>
       <c r="E61" s="3">
+        <v>45956900</v>
+      </c>
+      <c r="F61" s="3">
         <v>37363900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>36877400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>34442800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>33486400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>32266600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>31005200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>30711100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>23515400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>18935400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>17671200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>14312800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>14396600</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>3999600</v>
+        <v>4031700</v>
       </c>
       <c r="E62" s="3">
+        <v>4882500</v>
+      </c>
+      <c r="F62" s="3">
         <v>3668500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3645200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3485300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3146400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3104300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3714300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>8829500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>6624800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>4845300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>4194700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3841500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>4414200</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2971,9 +3119,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3016,9 +3167,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3061,54 +3215,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>55519000</v>
+      </c>
+      <c r="E66" s="3">
         <v>65140100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>59280900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>55964100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>52446200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>51565300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>49780100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>47213900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>46378900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>36011200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>30974100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>27230800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>23654200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>23464800</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3126,8 +3286,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3170,9 +3331,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3215,54 +3379,60 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>1736800</v>
+      </c>
+      <c r="E70" s="3">
         <v>1892300</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>1846400</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>2755500</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>3123500</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>3068500</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>2916700</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>3173600</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>2893500</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>1876400</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="3">
         <v>1770300</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="3">
         <v>1395700</v>
       </c>
-      <c r="O70" s="3">
+      <c r="P70" s="3">
         <v>921400</v>
       </c>
-      <c r="P70" s="3">
+      <c r="Q70" s="3">
         <v>1880600</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3305,54 +3475,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-3642500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-2269400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>605100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2981500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>4212100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>3049300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2032200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1294200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>827300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2079100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>4300500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3923000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>3528300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>3555400</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3395,9 +3571,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3440,9 +3619,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3485,54 +3667,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>17439700</v>
+      </c>
+      <c r="E76" s="3">
         <v>20485700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>23267700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>23535500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>21517800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>20649400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>18583600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>16792400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>14741600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>10466200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>13200600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>12865200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>11809000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>11021100</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3575,104 +3763,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41274</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40908</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3265100</v>
+      </c>
+      <c r="E81" s="3">
         <v>2212600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>552700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1544900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>3622700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3191900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2713000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2517400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>90100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-931100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1368300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1317900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>977900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1172300</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3690,53 +3887,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1937700</v>
+      </c>
+      <c r="E83" s="3">
         <v>2103500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1909200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1992900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2032600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1899700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1722200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1638700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1409700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1325300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1264700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1143200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1035100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1020200</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3779,9 +3980,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3824,9 +4028,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3869,9 +4076,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3914,9 +4124,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3959,54 +4172,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>5348800</v>
+      </c>
+      <c r="E89" s="3">
         <v>5503400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>4710300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>5444500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>5539200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>5460100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>4803800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>4170400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3685200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3089800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3202200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2828300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2688200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2831700</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4024,53 +4243,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-4418800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-6170500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-4970400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-4681200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-6384400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-6308200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-7265500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-6003600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3854600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3325600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3420500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3434200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1953500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1930600</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4113,9 +4336,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4158,54 +4384,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-4801800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-9303900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-5178700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-6094100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-4749600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-5298200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-7342400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2949600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-13655400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3461500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-3253200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-3941500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2451100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2346200</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4223,53 +4455,57 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>2747400</v>
+      </c>
+      <c r="E96" s="3">
         <v>2110400</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>2358500</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>2621100</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>2344200</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>1386200</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>1151300</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>1067700</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-1116700</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-1154800</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-1129700</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-1043900</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-964300</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-1561000</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4312,9 +4548,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4357,9 +4596,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4402,142 +4644,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2692400</v>
+      </c>
+      <c r="E100" s="3">
         <v>6128100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>359800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-69500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-627800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>534300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>2013900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1131500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>10183200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>558600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-292800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1381100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-303400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-493200</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>146000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-12100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>69500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>41900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-14900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-4600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>53500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-31100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-92300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>84100</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
       <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3">
         <v>21600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-11300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>3100</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1999500</v>
+      </c>
+      <c r="E102" s="3">
         <v>2315600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-39200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-677200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>146800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>691600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-471200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>58200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>120700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>271100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-343900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>289500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-77500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/TRP_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/TRP_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="92">
   <si>
     <t>TRP</t>
   </si>
@@ -656,221 +656,233 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42004</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41639</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41274</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40908</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>11114300</v>
+      </c>
+      <c r="E8" s="3">
         <v>9570900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>10046000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>9094700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>10578500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>10201700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>10219500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>10024600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>10724200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>9121800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>8524500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>7995700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>6772100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>6027600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>6022200</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>3124000</v>
+        <v>3442400</v>
       </c>
       <c r="E9" s="3">
-        <v>3019000</v>
+        <v>3140700</v>
       </c>
       <c r="F9" s="3">
+        <v>3144700</v>
+      </c>
+      <c r="G9" s="3">
         <v>3140200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>3243000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>3043500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3216600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3660600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>4939900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2807000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2480100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2334000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2058500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1939900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2572800</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>6446900</v>
+        <v>7671800</v>
       </c>
       <c r="E10" s="3">
-        <v>7026900</v>
+        <v>6430200</v>
       </c>
       <c r="F10" s="3">
+        <v>6901300</v>
+      </c>
+      <c r="G10" s="3">
         <v>5954500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>7335500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>7158200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>7002900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>6364000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>5784300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>6314800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>6044400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>5661800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4713600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>4087600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>3449400</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -889,8 +901,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -936,9 +949,12 @@
       <c r="Q12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -984,47 +1000,50 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-421900</v>
+        <v>-15300</v>
       </c>
       <c r="E14" s="3">
-        <v>1629500</v>
+        <v>-438500</v>
       </c>
       <c r="F14" s="3">
+        <v>1580300</v>
+      </c>
+      <c r="G14" s="3">
         <v>2679100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>2782300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>38500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>93300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>462400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>499200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1088300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>2827700</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>8</v>
+      <c r="O14" s="3">
+        <v>0</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>8</v>
@@ -1032,57 +1051,63 @@
       <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>2019500</v>
+      </c>
+      <c r="E15" s="3">
         <v>1761800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1852100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1671300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1992900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>2032600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1899700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1722200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1638700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1409700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1325300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1264700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1143200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>1035100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>1020200</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1098,104 +1123,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>5532900</v>
+        <v>6182500</v>
       </c>
       <c r="E17" s="3">
-        <v>5539000</v>
+        <v>5549600</v>
       </c>
       <c r="F17" s="3">
+        <v>5588200</v>
+      </c>
+      <c r="G17" s="3">
         <v>5348700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>5299900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>5646700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5758500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5861300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>7106400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>7287500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>8701000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5411300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4558100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4091400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3908000</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>4038000</v>
+        <v>4931700</v>
       </c>
       <c r="E18" s="3">
-        <v>4506900</v>
+        <v>4021300</v>
       </c>
       <c r="F18" s="3">
+        <v>4457700</v>
+      </c>
+      <c r="G18" s="3">
         <v>3746100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>5278600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>4555000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>4460900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>4163300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3617800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1834200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-176500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2584400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2214000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1936200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2114200</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1214,248 +1246,264 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1374100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1525500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1669700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-874100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-928500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1095600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1305300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-723300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1040600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>143200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>461800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>573100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>501900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-310900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>399500</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>7325300</v>
+        <v>8325300</v>
       </c>
       <c r="E21" s="3">
-        <v>8028700</v>
+        <v>7308700</v>
       </c>
       <c r="F21" s="3">
+        <v>7979500</v>
+      </c>
+      <c r="G21" s="3">
         <v>6291500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>8200000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>7683300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>7665900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>6608800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>6297000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3395100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1590200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>4417500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3857100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2660800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>3538700</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>2484800</v>
+      </c>
+      <c r="E22" s="3">
         <v>2098200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>2245900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1699400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1864900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1748500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1798700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1659900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1649800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1369000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1115800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>940500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>774400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>166400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>758200</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3970500</v>
+      </c>
+      <c r="E23" s="3">
         <v>4104700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2497300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>350200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1711600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>4008000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>3999100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2894000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2636200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>608500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-830500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2217000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1941500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1458900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1755400</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>830000</v>
+      </c>
+      <c r="E24" s="3">
         <v>640800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>637600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>237900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>94800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>152300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>581300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>316600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-71000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>255900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>25500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>652400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>470400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>350800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>441700</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1501,105 +1549,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3140500</v>
+      </c>
+      <c r="E26" s="3">
         <v>3463900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1859700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>112300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1616800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3855800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>3417800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2577400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2707200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>352600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-856000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1564600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1471100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1108100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1313700</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2479700</v>
+      </c>
+      <c r="E27" s="3">
         <v>3192800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>2142200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>473600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1434200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>3497900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>3065400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2593600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2389800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>90100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-931100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1368300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1317900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>977900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1172300</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1645,24 +1702,27 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>-154600</v>
+      </c>
+      <c r="E29" s="3">
         <v>274500</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>463400</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>467700</v>
       </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
       <c r="H29" s="3">
         <v>0</v>
       </c>
@@ -1681,8 +1741,8 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-      <c r="N29" s="3" t="s">
-        <v>8</v>
+      <c r="N29" s="3">
+        <v>0</v>
       </c>
       <c r="O29" s="3" t="s">
         <v>8</v>
@@ -1693,9 +1753,12 @@
       <c r="Q29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1741,9 +1804,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1789,105 +1855,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1374100</v>
+      </c>
+      <c r="E32" s="3">
         <v>1525500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1669700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>874100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>928500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1095600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1305300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>723300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1040600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-143200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-461800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-573100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-501900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>310900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-399500</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2566500</v>
+      </c>
+      <c r="E33" s="3">
         <v>3265100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2212600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>552700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1544900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3622700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>3191900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2713000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2517400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>90100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-931100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1368300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1317900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>977900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1172300</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1933,110 +2008,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2566500</v>
+      </c>
+      <c r="E35" s="3">
         <v>3265100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2212600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>552700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1544900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3622700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>3191900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2713000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2517400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>90100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-931100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1368300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1317900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>977900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1172300</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42004</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41639</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41274</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40908</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2055,8 +2139,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2075,85 +2160,89 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>122500</v>
+      </c>
+      <c r="E41" s="3">
         <v>556700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2785000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>458100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>531800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1200800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1035400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>326900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>868400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>738600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>638200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>383900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>713600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>414800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>502400</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>301200</v>
+      </c>
+      <c r="E42" s="3">
         <v>228700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>431600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>449200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>125600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>147500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>138800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>527700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>257600</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M42" s="3" t="s">
         <v>8</v>
@@ -2167,348 +2256,372 @@
       <c r="P42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3111300</v>
+      </c>
+      <c r="E43" s="3">
         <v>2160800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2183800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3373700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4070400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1800300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1985300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1974300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2011000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1508500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1041400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1030800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>863700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>791900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>840400</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>570300</v>
+      </c>
+      <c r="E44" s="3">
         <v>519200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>583800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>691600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>572100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>493600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>348500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>315900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>301400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>267500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>242500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>229200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>193200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>168600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>190500</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>373400</v>
+      </c>
+      <c r="E45" s="3">
         <v>370400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2539700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>279300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>261600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>229200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2304500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>548200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>127600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3362400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1537800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1935100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>652000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>750500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>855800</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4606500</v>
+      </c>
+      <c r="E46" s="3">
         <v>3984500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>8611000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5417400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5865700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4081800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5898800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3763200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3731800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5877100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2941900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2443900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2422600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2125900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2389200</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>8383700</v>
+      </c>
+      <c r="E47" s="3">
         <v>7470600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>7084500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>7102000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>6682800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>5255100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>5017600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>5256000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>5134400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>4843300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>4879800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>4583100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>4660500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>4327800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>4236000</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>51821900</v>
+      </c>
+      <c r="E48" s="3">
         <v>53863500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>52589300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>56109700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>55458400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>54759800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>50491300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>48736600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>45672500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>39603900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>67302600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>65589400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>28949900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>25378800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>93656500</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>9493000</v>
+      </c>
+      <c r="E49" s="3">
         <v>9500700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>9489400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>9489300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>9942400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>9950600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>9935700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>10390300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>10433100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>10147600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5981400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4603500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3534200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2886200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4594800</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2554,9 +2667,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2602,57 +2718,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>5672000</v>
+      </c>
+      <c r="E52" s="3">
         <v>4918500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>13844900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3916700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3617600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3329100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2664500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2377400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2224700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3542000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3169400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1733400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1924500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1665900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1738500</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2698,57 +2820,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>86608800</v>
+      </c>
+      <c r="E54" s="3">
         <v>82179400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>94677500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>84488200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>82353900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>78716100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>76543000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>72493300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>68656700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>64014000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>48353900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>45945100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>41491800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>36384600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>36366500</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2767,8 +2895,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2787,296 +2916,315 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2379800</v>
+      </c>
+      <c r="E57" s="3">
         <v>2570800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2341300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3446800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3527500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2673000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2555100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2362700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2270200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2006500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2745900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1274900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>666700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>694800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>534700</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2308300</v>
+      </c>
+      <c r="E58" s="3">
         <v>2379000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2281500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>6088300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>5171900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>4885400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>5446300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4563400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3694300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1899000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2827000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>3347500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2167000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2385600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2174900</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1779900</v>
+        <v>1767900</v>
       </c>
       <c r="E59" s="3">
+        <v>1627700</v>
+      </c>
+      <c r="F59" s="3">
         <v>3633900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2436100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1090500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1382000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1471000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2087900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1428900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1677900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1528000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1331400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1291000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1346700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1558000</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7263400</v>
+      </c>
+      <c r="E60" s="3">
         <v>7305200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>8948000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>12492100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>10305100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>9407500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>9945000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>9487400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>7875900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5583400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>5527800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>5950700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4124700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>4427200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>4242200</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>42196200</v>
+      </c>
+      <c r="E61" s="3">
         <v>39332400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>45956900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>37363900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>36877400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>34442800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>33486400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>32266600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>31005200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>30711100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>23515400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>18935400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>17671200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>14312800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>14396600</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4588200</v>
+      </c>
+      <c r="E62" s="3">
         <v>4031700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4882500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3668500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3645200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3485300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3146400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3104300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3714300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>8829500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>6624800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>4845300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>4194700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3841500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>4414200</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3122,9 +3270,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3170,9 +3321,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3218,57 +3372,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>59697200</v>
+      </c>
+      <c r="E66" s="3">
         <v>55519000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>65140100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>59280900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>55964100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>52446200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>51565300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>49780100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>47213900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>46378900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>36011200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>30974100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>27230800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>23654200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>23464800</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3287,8 +3447,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3334,9 +3495,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3382,57 +3546,63 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>1644600</v>
+      </c>
+      <c r="E70" s="3">
         <v>1736800</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>1892300</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>1846400</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>2755500</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>3123500</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>3068500</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>2916700</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>3173600</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>2893500</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="3">
         <v>1876400</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="3">
         <v>1770300</v>
       </c>
-      <c r="O70" s="3">
+      <c r="P70" s="3">
         <v>1395700</v>
       </c>
-      <c r="P70" s="3">
+      <c r="Q70" s="3">
         <v>921400</v>
       </c>
-      <c r="Q70" s="3">
+      <c r="R70" s="3">
         <v>1880600</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3478,57 +3648,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-4321300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-3642500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-2269400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>605100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2981500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>4212100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>3049300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2032200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1294200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>827300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2079100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>4300500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>3923000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>3528300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>3555400</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3574,9 +3750,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3622,9 +3801,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3670,57 +3852,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>18262400</v>
+      </c>
+      <c r="E76" s="3">
         <v>17439700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>20485700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>23267700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>23535500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>21517800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>20649400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>18583600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>16792400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>14741600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>10466200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>13200600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>12865200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>11809000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>11021100</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3766,110 +3954,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42004</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41639</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41274</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40908</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2566500</v>
+      </c>
+      <c r="E81" s="3">
         <v>3265100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2212600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>552700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1544900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3622700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>3191900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2713000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2517400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>90100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-931100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1368300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1317900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>977900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1172300</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3888,56 +4085,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1937700</v>
+        <v>2019500</v>
       </c>
       <c r="E83" s="3">
-        <v>2103500</v>
+        <v>1761800</v>
       </c>
       <c r="F83" s="3">
+        <v>1852100</v>
+      </c>
+      <c r="G83" s="3">
         <v>1909200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1992900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2032600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1899700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1722200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1638700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1409700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1325300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1264700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1143200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1035100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1020200</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3983,9 +4184,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4031,9 +4235,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4079,9 +4286,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4127,9 +4337,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4175,57 +4388,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>5357700</v>
+      </c>
+      <c r="E89" s="3">
         <v>5348800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>5503400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>4710300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>5444500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>5539200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>5460100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>4803800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>4170400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3685200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3089800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3202200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2828300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2688200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2831700</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4244,56 +4463,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3855200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4418800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-6170500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-4970400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-4681200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-6384400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-6308200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-7265500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-6003600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3854600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3325600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3420500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3434200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1953500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1930600</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4339,9 +4562,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4387,57 +4613,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-4710000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4801800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-9303900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-5178700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-6094100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-4749600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-5298200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-7342400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2949600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-13655400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-3461500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-3253200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3941500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2451100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2346200</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4456,56 +4688,60 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>2557800</v>
+      </c>
+      <c r="E96" s="3">
         <v>2747400</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>2110400</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>2358500</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>2621100</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>2344200</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>1386200</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>1151300</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>1067700</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-1116700</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-1154800</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-1129700</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-1043900</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-964300</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-1561000</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4551,9 +4787,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4599,9 +4838,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4647,151 +4889,163 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1105700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2692400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>6128100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>359800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-69500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-627800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>534300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>2013900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1131500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>10183200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>558600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-292800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1381100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-303400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-493200</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E101" s="3">
         <v>146000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-12100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>69500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>41900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-14900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-4600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>53500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-31100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-92300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>84100</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
       <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
         <v>21600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-11300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>3100</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-461700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1999500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2315600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-39200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-677200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>146800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>691600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-471200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>58200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>120700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>271100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-343900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>289500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-77500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-4600</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
